--- a/AAII_Financials/Yearly/BTI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BTI_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
   <si>
     <t>BTI</t>
   </si>
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>34308800</v>
+        <v>34788600</v>
       </c>
       <c r="E8" s="3">
-        <v>31863600</v>
+        <v>35262900</v>
       </c>
       <c r="F8" s="3">
-        <v>31977700</v>
+        <v>32749700</v>
       </c>
       <c r="G8" s="3">
-        <v>32103000</v>
+        <v>32867000</v>
       </c>
       <c r="H8" s="3">
-        <v>30384800</v>
+        <v>32995800</v>
       </c>
       <c r="I8" s="3">
-        <v>24271100</v>
+        <v>31229700</v>
       </c>
       <c r="J8" s="3">
+        <v>24946100</v>
+      </c>
+      <c r="K8" s="3">
         <v>17529700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15348700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18596800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20317200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19637800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20277200</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>5959800</v>
+        <v>6236500</v>
       </c>
       <c r="E9" s="3">
-        <v>5703000</v>
+        <v>6125600</v>
       </c>
       <c r="F9" s="3">
-        <v>5133600</v>
+        <v>5861600</v>
       </c>
       <c r="G9" s="3">
-        <v>5504500</v>
+        <v>5276400</v>
       </c>
       <c r="H9" s="3">
-        <v>5644700</v>
+        <v>5657600</v>
       </c>
       <c r="I9" s="3">
-        <v>6243900</v>
+        <v>5801700</v>
       </c>
       <c r="J9" s="3">
+        <v>6417600</v>
+      </c>
+      <c r="K9" s="3">
         <v>4631200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3552600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4033200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4317700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4281800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4511300</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>28349000</v>
+        <v>28552000</v>
       </c>
       <c r="E10" s="3">
-        <v>26160500</v>
+        <v>29137300</v>
       </c>
       <c r="F10" s="3">
-        <v>26844100</v>
+        <v>26888000</v>
       </c>
       <c r="G10" s="3">
-        <v>26598500</v>
+        <v>27590600</v>
       </c>
       <c r="H10" s="3">
-        <v>24740000</v>
+        <v>27338100</v>
       </c>
       <c r="I10" s="3">
-        <v>18027200</v>
+        <v>25428000</v>
       </c>
       <c r="J10" s="3">
+        <v>18528500</v>
+      </c>
+      <c r="K10" s="3">
         <v>12898500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11796200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14563600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15999400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15356000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15765900</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -862,50 +874,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>171200</v>
+        <v>230800</v>
       </c>
       <c r="E12" s="3">
-        <v>174900</v>
+        <v>176000</v>
       </c>
       <c r="F12" s="3">
-        <v>150100</v>
+        <v>179800</v>
       </c>
       <c r="G12" s="3">
-        <v>156300</v>
+        <v>154300</v>
       </c>
       <c r="H12" s="3">
-        <v>130300</v>
+        <v>160700</v>
       </c>
       <c r="I12" s="3">
-        <v>99200</v>
+        <v>133900</v>
       </c>
       <c r="J12" s="3">
+        <v>102000</v>
+      </c>
+      <c r="K12" s="3">
         <v>65800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>70300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>98500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>121200</v>
       </c>
-      <c r="N12" s="3" t="s">
+      <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>106700</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,93 +961,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1009800</v>
+        <v>36002400</v>
       </c>
       <c r="E14" s="3">
-        <v>805100</v>
+        <v>1037900</v>
       </c>
       <c r="F14" s="3">
-        <v>945300</v>
+        <v>827500</v>
       </c>
       <c r="G14" s="3">
-        <v>945300</v>
+        <v>971600</v>
       </c>
       <c r="H14" s="3">
-        <v>398200</v>
+        <v>971600</v>
       </c>
       <c r="I14" s="3">
-        <v>-27956900</v>
+        <v>409300</v>
       </c>
       <c r="J14" s="3">
+        <v>-28734400</v>
+      </c>
+      <c r="K14" s="3">
         <v>873400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>549300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1099500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>358100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>46500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>686000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1210800</v>
+        <v>1100400</v>
       </c>
       <c r="E15" s="3">
-        <v>1177300</v>
+        <v>1244500</v>
       </c>
       <c r="F15" s="3">
-        <v>1352300</v>
+        <v>1210100</v>
       </c>
       <c r="G15" s="3">
-        <v>1557000</v>
+        <v>1389900</v>
       </c>
       <c r="H15" s="3">
-        <v>1228200</v>
+        <v>1600300</v>
       </c>
       <c r="I15" s="3">
-        <v>1013600</v>
+        <v>1262300</v>
       </c>
       <c r="J15" s="3">
+        <v>1041800</v>
+      </c>
+      <c r="K15" s="3">
         <v>1346100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>473200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>640300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>589800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>764100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>679500</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>21254000</v>
+        <v>54712000</v>
       </c>
       <c r="E17" s="3">
-        <v>19167300</v>
+        <v>21845000</v>
       </c>
       <c r="F17" s="3">
-        <v>19795000</v>
+        <v>19700300</v>
       </c>
       <c r="G17" s="3">
-        <v>20917800</v>
+        <v>20345500</v>
       </c>
       <c r="H17" s="3">
-        <v>18775200</v>
+        <v>21499500</v>
       </c>
       <c r="I17" s="3">
-        <v>-12384900</v>
+        <v>19297400</v>
       </c>
       <c r="J17" s="3">
+        <v>-12729300</v>
+      </c>
+      <c r="K17" s="3">
         <v>11880000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10132900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12540300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12959800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12692800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14060700</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>13054800</v>
+        <v>-19923400</v>
       </c>
       <c r="E18" s="3">
-        <v>12696300</v>
+        <v>13417900</v>
       </c>
       <c r="F18" s="3">
-        <v>12182700</v>
+        <v>13049400</v>
       </c>
       <c r="G18" s="3">
-        <v>11185200</v>
+        <v>12521500</v>
       </c>
       <c r="H18" s="3">
-        <v>11609500</v>
+        <v>11496300</v>
       </c>
       <c r="I18" s="3">
-        <v>36656000</v>
+        <v>11932400</v>
       </c>
       <c r="J18" s="3">
+        <v>37675400</v>
+      </c>
+      <c r="K18" s="3">
         <v>5649700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5215800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6056500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7357300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6945000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6216600</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,218 +1179,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>531000</v>
+        <v>508800</v>
       </c>
       <c r="E20" s="3">
-        <v>482600</v>
+        <v>545700</v>
       </c>
       <c r="F20" s="3">
-        <v>599200</v>
+        <v>496000</v>
       </c>
       <c r="G20" s="3">
-        <v>749300</v>
+        <v>615900</v>
       </c>
       <c r="H20" s="3">
-        <v>727000</v>
+        <v>770200</v>
       </c>
       <c r="I20" s="3">
-        <v>1316300</v>
+        <v>747200</v>
       </c>
       <c r="J20" s="3">
+        <v>1352900</v>
+      </c>
+      <c r="K20" s="3">
         <v>2898000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2322700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1179400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1181000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1782800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1023100</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>15206400</v>
+        <v>17200100</v>
       </c>
       <c r="E21" s="3">
-        <v>14515100</v>
+        <v>15633500</v>
       </c>
       <c r="F21" s="3">
-        <v>14395000</v>
+        <v>14922200</v>
       </c>
       <c r="G21" s="3">
-        <v>13733900</v>
+        <v>14799600</v>
       </c>
       <c r="H21" s="3">
-        <v>13565900</v>
+        <v>14120600</v>
       </c>
       <c r="I21" s="3">
-        <v>38986800</v>
+        <v>13946400</v>
       </c>
       <c r="J21" s="3">
+        <v>40073700</v>
+      </c>
+      <c r="K21" s="3">
         <v>9301500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8024500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7933500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9175300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9345300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8311500</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2018500</v>
+        <v>2339800</v>
       </c>
       <c r="E22" s="3">
-        <v>1811300</v>
+        <v>2074600</v>
       </c>
       <c r="F22" s="3">
-        <v>2023400</v>
+        <v>1861600</v>
       </c>
       <c r="G22" s="3">
-        <v>2118900</v>
+        <v>2079700</v>
       </c>
       <c r="H22" s="3">
-        <v>1976300</v>
+        <v>2177900</v>
       </c>
       <c r="I22" s="3">
-        <v>1341100</v>
+        <v>2031200</v>
       </c>
       <c r="J22" s="3">
+        <v>1378400</v>
+      </c>
+      <c r="K22" s="3">
         <v>800200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>680500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>782700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>817500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1498400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>746600</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>11567400</v>
+        <v>-21754500</v>
       </c>
       <c r="E23" s="3">
-        <v>11367600</v>
+        <v>11889000</v>
       </c>
       <c r="F23" s="3">
-        <v>10758500</v>
+        <v>11683700</v>
       </c>
       <c r="G23" s="3">
-        <v>9815600</v>
+        <v>11057700</v>
       </c>
       <c r="H23" s="3">
-        <v>10360300</v>
+        <v>10088600</v>
       </c>
       <c r="I23" s="3">
-        <v>36631200</v>
+        <v>10648400</v>
       </c>
       <c r="J23" s="3">
+        <v>37649900</v>
+      </c>
+      <c r="K23" s="3">
         <v>7747500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6858000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6453200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7720800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7229400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6493100</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>3074200</v>
+        <v>-3662100</v>
       </c>
       <c r="E24" s="3">
-        <v>2911700</v>
+        <v>3159700</v>
       </c>
       <c r="F24" s="3">
-        <v>2780200</v>
+        <v>2992700</v>
       </c>
       <c r="G24" s="3">
-        <v>2617700</v>
+        <v>2857500</v>
       </c>
       <c r="H24" s="3">
-        <v>2743000</v>
+        <v>2690500</v>
       </c>
       <c r="I24" s="3">
-        <v>1807600</v>
+        <v>2819200</v>
       </c>
       <c r="J24" s="3">
+        <v>1857800</v>
+      </c>
+      <c r="K24" s="3">
         <v>1744300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1561300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1936800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2130200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1959900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2048900</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>8493100</v>
+        <v>-18092400</v>
       </c>
       <c r="E26" s="3">
-        <v>8455900</v>
+        <v>8729300</v>
       </c>
       <c r="F26" s="3">
-        <v>7978300</v>
+        <v>8691100</v>
       </c>
       <c r="G26" s="3">
-        <v>7198000</v>
+        <v>8200200</v>
       </c>
       <c r="H26" s="3">
-        <v>7617300</v>
+        <v>7398100</v>
       </c>
       <c r="I26" s="3">
-        <v>34823600</v>
+        <v>7829100</v>
       </c>
       <c r="J26" s="3">
+        <v>35792100</v>
+      </c>
+      <c r="K26" s="3">
         <v>6003300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5296600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4516400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5590500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5269500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4444200</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>8269800</v>
+        <v>-18319400</v>
       </c>
       <c r="E27" s="3">
-        <v>8241300</v>
+        <v>8499800</v>
       </c>
       <c r="F27" s="3">
-        <v>7774800</v>
+        <v>8470500</v>
       </c>
       <c r="G27" s="3">
-        <v>7018100</v>
+        <v>7991100</v>
       </c>
       <c r="H27" s="3">
-        <v>7396500</v>
+        <v>7213200</v>
       </c>
       <c r="I27" s="3">
-        <v>34611500</v>
+        <v>7602100</v>
       </c>
       <c r="J27" s="3">
+        <v>35574000</v>
+      </c>
+      <c r="K27" s="3">
         <v>5766300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5024900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4146400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5197800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4908800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4075500</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,35 +1581,38 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="3">
-        <v>196000</v>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F29" s="3">
-        <v>165000</v>
+        <v>201500</v>
       </c>
       <c r="G29" s="3">
-        <v>58300</v>
+        <v>169600</v>
       </c>
       <c r="H29" s="3">
-        <v>86800</v>
+        <v>59900</v>
       </c>
       <c r="I29" s="3">
-        <v>11892400</v>
+        <v>89300</v>
       </c>
       <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+        <v>12223100</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-531000</v>
+        <v>-508800</v>
       </c>
       <c r="E32" s="3">
-        <v>-482600</v>
+        <v>-545700</v>
       </c>
       <c r="F32" s="3">
-        <v>-599200</v>
+        <v>-496000</v>
       </c>
       <c r="G32" s="3">
-        <v>-749300</v>
+        <v>-615900</v>
       </c>
       <c r="H32" s="3">
-        <v>-727000</v>
+        <v>-770200</v>
       </c>
       <c r="I32" s="3">
-        <v>-1316300</v>
+        <v>-747200</v>
       </c>
       <c r="J32" s="3">
+        <v>-1352900</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2898000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2322700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1179400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1181000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1782800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1023100</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>8269800</v>
+        <v>-18319400</v>
       </c>
       <c r="E33" s="3">
-        <v>8437300</v>
+        <v>8499800</v>
       </c>
       <c r="F33" s="3">
-        <v>7939800</v>
+        <v>8672000</v>
       </c>
       <c r="G33" s="3">
-        <v>7076400</v>
+        <v>8160600</v>
       </c>
       <c r="H33" s="3">
-        <v>7483300</v>
+        <v>7273200</v>
       </c>
       <c r="I33" s="3">
-        <v>46503900</v>
+        <v>7691400</v>
       </c>
       <c r="J33" s="3">
+        <v>47797100</v>
+      </c>
+      <c r="K33" s="3">
         <v>5766300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5024900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4146400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5197800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4908800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4075500</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>8269800</v>
+        <v>-18319400</v>
       </c>
       <c r="E35" s="3">
-        <v>8437300</v>
+        <v>8499800</v>
       </c>
       <c r="F35" s="3">
-        <v>7939800</v>
+        <v>8672000</v>
       </c>
       <c r="G35" s="3">
-        <v>7076400</v>
+        <v>8160600</v>
       </c>
       <c r="H35" s="3">
-        <v>7483300</v>
+        <v>7273200</v>
       </c>
       <c r="I35" s="3">
-        <v>46503900</v>
+        <v>7691400</v>
       </c>
       <c r="J35" s="3">
+        <v>47797100</v>
+      </c>
+      <c r="K35" s="3">
         <v>5766300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5024900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4146400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5197800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4908800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4075500</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,386 +1987,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4275100</v>
+        <v>5940700</v>
       </c>
       <c r="E41" s="3">
-        <v>3484800</v>
+        <v>4394000</v>
       </c>
       <c r="F41" s="3">
-        <v>3894200</v>
+        <v>3581800</v>
       </c>
       <c r="G41" s="3">
-        <v>3133800</v>
+        <v>4002500</v>
       </c>
       <c r="H41" s="3">
-        <v>3228000</v>
+        <v>3220900</v>
       </c>
       <c r="I41" s="3">
-        <v>8165600</v>
+        <v>3317800</v>
       </c>
       <c r="J41" s="3">
+        <v>8392700</v>
+      </c>
+      <c r="K41" s="3">
         <v>2734300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2299300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2419900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2803900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1263100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1277300</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>718300</v>
+        <v>766300</v>
       </c>
       <c r="E42" s="3">
-        <v>565700</v>
+        <v>738300</v>
       </c>
       <c r="F42" s="3">
-        <v>300200</v>
+        <v>581400</v>
       </c>
       <c r="G42" s="3">
-        <v>152600</v>
+        <v>308600</v>
       </c>
       <c r="H42" s="3">
-        <v>220800</v>
+        <v>156800</v>
       </c>
       <c r="I42" s="3">
-        <v>80600</v>
+        <v>227000</v>
       </c>
       <c r="J42" s="3">
+        <v>82900</v>
+      </c>
+      <c r="K42" s="3">
         <v>18600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>41000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>66600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>71900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1460900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1686800</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5602500</v>
+        <v>4836500</v>
       </c>
       <c r="E43" s="3">
-        <v>5046800</v>
+        <v>5758400</v>
       </c>
       <c r="F43" s="3">
-        <v>4714300</v>
+        <v>5187100</v>
       </c>
       <c r="G43" s="3">
-        <v>5229100</v>
+        <v>4845400</v>
       </c>
       <c r="H43" s="3">
-        <v>4543100</v>
+        <v>5374500</v>
       </c>
       <c r="I43" s="3">
-        <v>5598800</v>
+        <v>4669400</v>
       </c>
       <c r="J43" s="3">
+        <v>5754500</v>
+      </c>
+      <c r="K43" s="3">
         <v>4904100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3912100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3760400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3955600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3650900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3357800</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>7035400</v>
+        <v>6296400</v>
       </c>
       <c r="E44" s="3">
-        <v>6549100</v>
+        <v>7231100</v>
       </c>
       <c r="F44" s="3">
-        <v>7441100</v>
+        <v>6731300</v>
       </c>
       <c r="G44" s="3">
-        <v>7560200</v>
+        <v>7648000</v>
       </c>
       <c r="H44" s="3">
-        <v>7479600</v>
+        <v>7770500</v>
       </c>
       <c r="I44" s="3">
-        <v>14549800</v>
+        <v>7687600</v>
       </c>
       <c r="J44" s="3">
+        <v>14954400</v>
+      </c>
+      <c r="K44" s="3">
         <v>7186800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4974500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5501400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5381500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5204900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4606100</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1485000</v>
+        <v>248600</v>
       </c>
       <c r="E45" s="3">
-        <v>241900</v>
+        <v>1526300</v>
       </c>
       <c r="F45" s="3">
-        <v>537200</v>
+        <v>248600</v>
       </c>
       <c r="G45" s="3">
-        <v>392000</v>
+        <v>552100</v>
       </c>
       <c r="H45" s="3">
-        <v>228300</v>
+        <v>402900</v>
       </c>
       <c r="I45" s="3">
-        <v>289100</v>
+        <v>234600</v>
       </c>
       <c r="J45" s="3">
+        <v>297100</v>
+      </c>
+      <c r="K45" s="3">
         <v>488800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>268200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>407300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>459300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>296100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>258100</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>19116400</v>
+        <v>18088600</v>
       </c>
       <c r="E46" s="3">
-        <v>15888400</v>
+        <v>19648000</v>
       </c>
       <c r="F46" s="3">
-        <v>16887000</v>
+        <v>16330200</v>
       </c>
       <c r="G46" s="3">
-        <v>16467700</v>
+        <v>17356700</v>
       </c>
       <c r="H46" s="3">
-        <v>15699800</v>
+        <v>16925700</v>
       </c>
       <c r="I46" s="3">
-        <v>17326200</v>
+        <v>16136400</v>
       </c>
       <c r="J46" s="3">
+        <v>17808000</v>
+      </c>
+      <c r="K46" s="3">
         <v>15332600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11495100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12155600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12672300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11875800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11186100</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2955100</v>
+        <v>3071700</v>
       </c>
       <c r="E47" s="3">
-        <v>2739200</v>
+        <v>3037300</v>
       </c>
       <c r="F47" s="3">
-        <v>2555600</v>
+        <v>2815400</v>
       </c>
       <c r="G47" s="3">
-        <v>2630100</v>
+        <v>2626700</v>
       </c>
       <c r="H47" s="3">
-        <v>3053100</v>
+        <v>2703200</v>
       </c>
       <c r="I47" s="3">
-        <v>2946400</v>
+        <v>3138000</v>
       </c>
       <c r="J47" s="3">
+        <v>3028400</v>
+      </c>
+      <c r="K47" s="3">
         <v>12590800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8460300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3446200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3336500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3349700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3895100</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6038000</v>
+        <v>5843800</v>
       </c>
       <c r="E48" s="3">
-        <v>6144700</v>
+        <v>6205900</v>
       </c>
       <c r="F48" s="3">
-        <v>6277400</v>
+        <v>6315600</v>
       </c>
       <c r="G48" s="3">
-        <v>6845600</v>
+        <v>6452000</v>
       </c>
       <c r="H48" s="3">
-        <v>6408900</v>
+        <v>7036000</v>
       </c>
       <c r="I48" s="3">
-        <v>12113200</v>
+        <v>6587200</v>
       </c>
       <c r="J48" s="3">
+        <v>12450100</v>
+      </c>
+      <c r="K48" s="3">
         <v>4541800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3538500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3998600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4201900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4138300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4012300</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>160130000</v>
+        <v>121851000</v>
       </c>
       <c r="E49" s="3">
-        <v>143444000</v>
+        <v>164584000</v>
       </c>
       <c r="F49" s="3">
-        <v>143095000</v>
+        <v>147433000</v>
       </c>
       <c r="G49" s="3">
-        <v>147367000</v>
+        <v>147074000</v>
       </c>
       <c r="H49" s="3">
-        <v>153851000</v>
+        <v>151465000</v>
       </c>
       <c r="I49" s="3">
-        <v>292248000</v>
+        <v>158129000</v>
       </c>
       <c r="J49" s="3">
+        <v>300375000</v>
+      </c>
+      <c r="K49" s="3">
         <v>15032400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12223700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14381200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14918300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15138800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15790900</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,51 +2479,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2249200</v>
+        <v>2519600</v>
       </c>
       <c r="E52" s="3">
-        <v>2198300</v>
+        <v>2311800</v>
       </c>
       <c r="F52" s="3">
-        <v>2003600</v>
+        <v>2259500</v>
       </c>
       <c r="G52" s="3">
-        <v>1620200</v>
+        <v>2059300</v>
       </c>
       <c r="H52" s="3">
-        <v>2539500</v>
+        <v>1665300</v>
       </c>
       <c r="I52" s="3">
-        <v>2538300</v>
+        <v>2610100</v>
       </c>
       <c r="J52" s="3">
+        <v>2608900</v>
+      </c>
+      <c r="K52" s="3">
         <v>1844800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1195900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>849200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>660400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>826100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>825600</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>190489000</v>
+        <v>151375000</v>
       </c>
       <c r="E54" s="3">
-        <v>170415000</v>
+        <v>195787000</v>
       </c>
       <c r="F54" s="3">
-        <v>170818000</v>
+        <v>175154000</v>
       </c>
       <c r="G54" s="3">
-        <v>174931000</v>
+        <v>175569000</v>
       </c>
       <c r="H54" s="3">
-        <v>181552000</v>
+        <v>179796000</v>
       </c>
       <c r="I54" s="3">
-        <v>174992000</v>
+        <v>186601000</v>
       </c>
       <c r="J54" s="3">
+        <v>179858000</v>
+      </c>
+      <c r="K54" s="3">
         <v>49342400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36913500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>34830900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>35789400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35328600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35710000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,260 +2655,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>12963000</v>
+        <v>12368500</v>
       </c>
       <c r="E57" s="3">
-        <v>11881200</v>
+        <v>13323500</v>
       </c>
       <c r="F57" s="3">
-        <v>12025100</v>
+        <v>12211600</v>
       </c>
       <c r="G57" s="3">
-        <v>12067300</v>
+        <v>12359500</v>
       </c>
       <c r="H57" s="3">
-        <v>13188800</v>
+        <v>12402900</v>
       </c>
       <c r="I57" s="3">
-        <v>11051300</v>
+        <v>13555600</v>
       </c>
       <c r="J57" s="3">
+        <v>11358600</v>
+      </c>
+      <c r="K57" s="3">
         <v>9099800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6954000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7353000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7643600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7533200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6813100</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4824700</v>
+        <v>4782900</v>
       </c>
       <c r="E58" s="3">
-        <v>4381800</v>
+        <v>4958900</v>
       </c>
       <c r="F58" s="3">
-        <v>4394200</v>
+        <v>4503700</v>
       </c>
       <c r="G58" s="3">
-        <v>8793400</v>
+        <v>4516400</v>
       </c>
       <c r="H58" s="3">
-        <v>4658500</v>
+        <v>9037900</v>
       </c>
       <c r="I58" s="3">
-        <v>12903500</v>
+        <v>4788000</v>
       </c>
       <c r="J58" s="3">
+        <v>13262300</v>
+      </c>
+      <c r="K58" s="3">
         <v>3730500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2571000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3299800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2636200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2115000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2325500</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4360700</v>
+        <v>2833300</v>
       </c>
       <c r="E59" s="3">
-        <v>2524600</v>
+        <v>4482000</v>
       </c>
       <c r="F59" s="3">
-        <v>2782700</v>
+        <v>2594800</v>
       </c>
       <c r="G59" s="3">
-        <v>2491100</v>
+        <v>2860000</v>
       </c>
       <c r="H59" s="3">
-        <v>2410500</v>
+        <v>2560400</v>
       </c>
       <c r="I59" s="3">
-        <v>2627600</v>
+        <v>2477500</v>
       </c>
       <c r="J59" s="3">
+        <v>2700700</v>
+      </c>
+      <c r="K59" s="3">
         <v>1878300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1023700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1019600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>952000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>877800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1194300</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>22148400</v>
+        <v>19984600</v>
       </c>
       <c r="E60" s="3">
-        <v>18787600</v>
+        <v>22764400</v>
       </c>
       <c r="F60" s="3">
-        <v>19202000</v>
+        <v>19310100</v>
       </c>
       <c r="G60" s="3">
-        <v>23351800</v>
+        <v>19736000</v>
       </c>
       <c r="H60" s="3">
-        <v>20257800</v>
+        <v>24001200</v>
       </c>
       <c r="I60" s="3">
-        <v>19359600</v>
+        <v>20821100</v>
       </c>
       <c r="J60" s="3">
+        <v>19897900</v>
+      </c>
+      <c r="K60" s="3">
         <v>14708600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10548700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11672400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11231700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10526100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10332900</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>48043500</v>
+        <v>45146200</v>
       </c>
       <c r="E61" s="3">
-        <v>44247200</v>
+        <v>49379500</v>
       </c>
       <c r="F61" s="3">
-        <v>49533400</v>
+        <v>45477700</v>
       </c>
       <c r="G61" s="3">
-        <v>46899600</v>
+        <v>50910900</v>
       </c>
       <c r="H61" s="3">
-        <v>53698100</v>
+        <v>48203900</v>
       </c>
       <c r="I61" s="3">
-        <v>54619900</v>
+        <v>55191400</v>
       </c>
       <c r="J61" s="3">
+        <v>56138800</v>
+      </c>
+      <c r="K61" s="3">
         <v>20455000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>17342300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13016800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12935900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11742600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11205900</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>26371400</v>
+        <v>18747800</v>
       </c>
       <c r="E62" s="3">
-        <v>23762500</v>
+        <v>27104800</v>
       </c>
       <c r="F62" s="3">
-        <v>23980800</v>
+        <v>24423300</v>
       </c>
       <c r="G62" s="3">
-        <v>25082500</v>
+        <v>24647700</v>
       </c>
       <c r="H62" s="3">
-        <v>26103500</v>
+        <v>25780000</v>
       </c>
       <c r="I62" s="3">
-        <v>25798300</v>
+        <v>26829400</v>
       </c>
       <c r="J62" s="3">
+        <v>26515700</v>
+      </c>
+      <c r="K62" s="3">
         <v>3750300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3128500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2402600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2388500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3003200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3012800</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>96987600</v>
+        <v>84347900</v>
       </c>
       <c r="E66" s="3">
-        <v>87169500</v>
+        <v>99684800</v>
       </c>
       <c r="F66" s="3">
-        <v>93066100</v>
+        <v>89593600</v>
       </c>
       <c r="G66" s="3">
-        <v>95654000</v>
+        <v>95654200</v>
       </c>
       <c r="H66" s="3">
-        <v>100362000</v>
+        <v>98314000</v>
       </c>
       <c r="I66" s="3">
-        <v>99614000</v>
+        <v>103153000</v>
       </c>
       <c r="J66" s="3">
+        <v>102384000</v>
+      </c>
+      <c r="K66" s="3">
         <v>39191800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>31181200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27496500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26956900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25668700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>24955800</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>97120400</v>
+        <v>74867500</v>
       </c>
       <c r="E72" s="3">
-        <v>94809100</v>
+        <v>99821200</v>
       </c>
       <c r="F72" s="3">
-        <v>92150500</v>
+        <v>97445700</v>
       </c>
       <c r="G72" s="3">
-        <v>90046500</v>
+        <v>94713200</v>
       </c>
       <c r="H72" s="3">
-        <v>87942400</v>
+        <v>92550600</v>
       </c>
       <c r="I72" s="3">
-        <v>127485000</v>
+        <v>90388000</v>
       </c>
       <c r="J72" s="3">
+        <v>131031000</v>
+      </c>
+      <c r="K72" s="3">
         <v>9419900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5047100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6561000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8064300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12568700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12030200</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>93501500</v>
+        <v>67026900</v>
       </c>
       <c r="E76" s="3">
-        <v>83245500</v>
+        <v>96101700</v>
       </c>
       <c r="F76" s="3">
-        <v>77752100</v>
+        <v>85560500</v>
       </c>
       <c r="G76" s="3">
-        <v>79276800</v>
+        <v>79914300</v>
       </c>
       <c r="H76" s="3">
-        <v>81189800</v>
+        <v>81481400</v>
       </c>
       <c r="I76" s="3">
-        <v>75377600</v>
+        <v>83447600</v>
       </c>
       <c r="J76" s="3">
+        <v>77473800</v>
+      </c>
+      <c r="K76" s="3">
         <v>10150600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5732300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7334400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8832500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9659900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10754200</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>8269800</v>
+        <v>-18319400</v>
       </c>
       <c r="E81" s="3">
-        <v>8437300</v>
+        <v>8499800</v>
       </c>
       <c r="F81" s="3">
-        <v>7939800</v>
+        <v>8672000</v>
       </c>
       <c r="G81" s="3">
-        <v>7076400</v>
+        <v>8160600</v>
       </c>
       <c r="H81" s="3">
-        <v>7483300</v>
+        <v>7273200</v>
       </c>
       <c r="I81" s="3">
-        <v>46503900</v>
+        <v>7691400</v>
       </c>
       <c r="J81" s="3">
+        <v>47797100</v>
+      </c>
+      <c r="K81" s="3">
         <v>5766300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5024900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4146400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5197800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4908800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4075500</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1619000</v>
+        <v>36485700</v>
       </c>
       <c r="E83" s="3">
-        <v>1334900</v>
+        <v>1664000</v>
       </c>
       <c r="F83" s="3">
-        <v>1611500</v>
+        <v>1372000</v>
       </c>
       <c r="G83" s="3">
-        <v>1797600</v>
+        <v>1656400</v>
       </c>
       <c r="H83" s="3">
-        <v>1228200</v>
+        <v>1847600</v>
       </c>
       <c r="I83" s="3">
-        <v>1013600</v>
+        <v>1262300</v>
       </c>
       <c r="J83" s="3">
+        <v>1041800</v>
+      </c>
+      <c r="K83" s="3">
         <v>753000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>501300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>696200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>635100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>614100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1075800</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>12438300</v>
+        <v>14130700</v>
       </c>
       <c r="E89" s="3">
-        <v>12054900</v>
+        <v>12784200</v>
       </c>
       <c r="F89" s="3">
-        <v>12140500</v>
+        <v>12390100</v>
       </c>
       <c r="G89" s="3">
-        <v>11160400</v>
+        <v>12478100</v>
       </c>
       <c r="H89" s="3">
-        <v>12772000</v>
+        <v>11470800</v>
       </c>
       <c r="I89" s="3">
-        <v>6633500</v>
+        <v>13127200</v>
       </c>
       <c r="J89" s="3">
+        <v>6818000</v>
+      </c>
+      <c r="K89" s="3">
         <v>5719200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5528500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4946400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5906100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5723300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6012500</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-648800</v>
+        <v>-586500</v>
       </c>
       <c r="E91" s="3">
-        <v>-653800</v>
+        <v>-666900</v>
       </c>
       <c r="F91" s="3">
-        <v>-633900</v>
+        <v>-672000</v>
       </c>
       <c r="G91" s="3">
-        <v>-823800</v>
+        <v>-651600</v>
       </c>
       <c r="H91" s="3">
-        <v>-940400</v>
+        <v>-846700</v>
       </c>
       <c r="I91" s="3">
-        <v>-981300</v>
+        <v>-966500</v>
       </c>
       <c r="J91" s="3">
+        <v>-1008600</v>
+      </c>
+      <c r="K91" s="3">
         <v>-727000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-565700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-704200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-764200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-858400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-671600</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-874600</v>
+        <v>-377400</v>
       </c>
       <c r="E94" s="3">
-        <v>-1414300</v>
+        <v>-898900</v>
       </c>
       <c r="F94" s="3">
-        <v>-971400</v>
+        <v>-1453600</v>
       </c>
       <c r="G94" s="3">
-        <v>-792700</v>
+        <v>-998400</v>
       </c>
       <c r="H94" s="3">
-        <v>-1266700</v>
+        <v>-814800</v>
       </c>
       <c r="I94" s="3">
-        <v>-23005700</v>
+        <v>-1301900</v>
       </c>
       <c r="J94" s="3">
+        <v>-23645500</v>
+      </c>
+      <c r="K94" s="3">
         <v>-794000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4674700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-625600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-446000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-517100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-937600</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,50 +4221,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-6097500</v>
+        <v>-6445600</v>
       </c>
       <c r="E96" s="3">
-        <v>-6083900</v>
+        <v>-6267100</v>
       </c>
       <c r="F96" s="3">
-        <v>-5886600</v>
+        <v>-6253100</v>
       </c>
       <c r="G96" s="3">
-        <v>-5704300</v>
+        <v>-6050300</v>
       </c>
       <c r="H96" s="3">
-        <v>-5392900</v>
+        <v>-5862900</v>
       </c>
       <c r="I96" s="3">
-        <v>-4298700</v>
+        <v>-5542900</v>
       </c>
       <c r="J96" s="3">
+        <v>-4418200</v>
+      </c>
+      <c r="K96" s="3">
         <v>-3610100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-3244500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3609900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3476300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3281200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3105000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,133 +4398,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-11014000</v>
+        <v>-11876300</v>
       </c>
       <c r="E100" s="3">
-        <v>-10854000</v>
+        <v>-11320300</v>
       </c>
       <c r="F100" s="3">
-        <v>-9797000</v>
+        <v>-11155800</v>
       </c>
       <c r="G100" s="3">
-        <v>-10660500</v>
+        <v>-10069500</v>
       </c>
       <c r="H100" s="3">
-        <v>-11947000</v>
+        <v>-10956900</v>
       </c>
       <c r="I100" s="3">
-        <v>18310000</v>
+        <v>-12279200</v>
       </c>
       <c r="J100" s="3">
+        <v>18819200</v>
+      </c>
+      <c r="K100" s="3">
         <v>-5246500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-256500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4614900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5281700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5111800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5329000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>534700</v>
+        <v>-372300</v>
       </c>
       <c r="E101" s="3">
-        <v>-313900</v>
+        <v>549600</v>
       </c>
       <c r="F101" s="3">
-        <v>-313900</v>
+        <v>-322600</v>
       </c>
       <c r="G101" s="3">
-        <v>-70700</v>
+        <v>-322600</v>
       </c>
       <c r="H101" s="3">
-        <v>-171200</v>
+        <v>-72700</v>
       </c>
       <c r="I101" s="3">
-        <v>-485100</v>
+        <v>-176000</v>
       </c>
       <c r="J101" s="3">
+        <v>-498600</v>
+      </c>
+      <c r="K101" s="3">
         <v>223300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-318600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-83900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-262300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-227500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-63200</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1084300</v>
+        <v>1973900</v>
       </c>
       <c r="E102" s="3">
-        <v>-527300</v>
+        <v>1114400</v>
       </c>
       <c r="F102" s="3">
-        <v>1058200</v>
+        <v>-541900</v>
       </c>
       <c r="G102" s="3">
-        <v>-363500</v>
+        <v>1087700</v>
       </c>
       <c r="H102" s="3">
-        <v>-612900</v>
+        <v>-373600</v>
       </c>
       <c r="I102" s="3">
-        <v>1452700</v>
+        <v>-629900</v>
       </c>
       <c r="J102" s="3">
+        <v>1493100</v>
+      </c>
+      <c r="K102" s="3">
         <v>-98000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>278800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-378000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-83900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-133200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-317300</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BTI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BTI_YR_FIN.xlsx
@@ -727,25 +727,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>34788600</v>
+        <v>34911600</v>
       </c>
       <c r="E8" s="3">
-        <v>35262900</v>
+        <v>35387600</v>
       </c>
       <c r="F8" s="3">
-        <v>32749700</v>
+        <v>32865500</v>
       </c>
       <c r="G8" s="3">
-        <v>32867000</v>
+        <v>32983200</v>
       </c>
       <c r="H8" s="3">
-        <v>32995800</v>
+        <v>33112500</v>
       </c>
       <c r="I8" s="3">
-        <v>31229700</v>
+        <v>31340200</v>
       </c>
       <c r="J8" s="3">
-        <v>24946100</v>
+        <v>25034300</v>
       </c>
       <c r="K8" s="3">
         <v>17529700</v>
@@ -772,25 +772,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6236500</v>
+        <v>6258600</v>
       </c>
       <c r="E9" s="3">
-        <v>6125600</v>
+        <v>6147200</v>
       </c>
       <c r="F9" s="3">
-        <v>5861600</v>
+        <v>5882400</v>
       </c>
       <c r="G9" s="3">
-        <v>5276400</v>
+        <v>5295000</v>
       </c>
       <c r="H9" s="3">
-        <v>5657600</v>
+        <v>5677600</v>
       </c>
       <c r="I9" s="3">
-        <v>5801700</v>
+        <v>5822200</v>
       </c>
       <c r="J9" s="3">
-        <v>6417600</v>
+        <v>6440300</v>
       </c>
       <c r="K9" s="3">
         <v>4631200</v>
@@ -817,25 +817,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>28552000</v>
+        <v>28653000</v>
       </c>
       <c r="E10" s="3">
-        <v>29137300</v>
+        <v>29240400</v>
       </c>
       <c r="F10" s="3">
-        <v>26888000</v>
+        <v>26983100</v>
       </c>
       <c r="G10" s="3">
-        <v>27590600</v>
+        <v>27688200</v>
       </c>
       <c r="H10" s="3">
-        <v>27338100</v>
+        <v>27434800</v>
       </c>
       <c r="I10" s="3">
-        <v>25428000</v>
+        <v>25518000</v>
       </c>
       <c r="J10" s="3">
-        <v>18528500</v>
+        <v>18594000</v>
       </c>
       <c r="K10" s="3">
         <v>12898500</v>
@@ -881,25 +881,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>230800</v>
+        <v>231600</v>
       </c>
       <c r="E12" s="3">
-        <v>176000</v>
+        <v>176600</v>
       </c>
       <c r="F12" s="3">
-        <v>179800</v>
+        <v>180400</v>
       </c>
       <c r="G12" s="3">
-        <v>154300</v>
+        <v>154800</v>
       </c>
       <c r="H12" s="3">
-        <v>160700</v>
+        <v>161200</v>
       </c>
       <c r="I12" s="3">
-        <v>133900</v>
+        <v>134400</v>
       </c>
       <c r="J12" s="3">
-        <v>102000</v>
+        <v>102400</v>
       </c>
       <c r="K12" s="3">
         <v>65800</v>
@@ -971,25 +971,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>36002400</v>
+        <v>36129800</v>
       </c>
       <c r="E14" s="3">
-        <v>1037900</v>
+        <v>1041600</v>
       </c>
       <c r="F14" s="3">
-        <v>827500</v>
+        <v>830500</v>
       </c>
       <c r="G14" s="3">
-        <v>971600</v>
+        <v>975100</v>
       </c>
       <c r="H14" s="3">
-        <v>971600</v>
+        <v>975100</v>
       </c>
       <c r="I14" s="3">
-        <v>409300</v>
+        <v>410800</v>
       </c>
       <c r="J14" s="3">
-        <v>-28734400</v>
+        <v>-28836000</v>
       </c>
       <c r="K14" s="3">
         <v>873400</v>
@@ -1016,25 +1016,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1100400</v>
+        <v>1104300</v>
       </c>
       <c r="E15" s="3">
-        <v>1244500</v>
+        <v>1248900</v>
       </c>
       <c r="F15" s="3">
-        <v>1210100</v>
+        <v>1214300</v>
       </c>
       <c r="G15" s="3">
-        <v>1389900</v>
+        <v>1394800</v>
       </c>
       <c r="H15" s="3">
-        <v>1600300</v>
+        <v>1605900</v>
       </c>
       <c r="I15" s="3">
-        <v>1262300</v>
+        <v>1266800</v>
       </c>
       <c r="J15" s="3">
-        <v>1041800</v>
+        <v>1045400</v>
       </c>
       <c r="K15" s="3">
         <v>1346100</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>54712000</v>
+        <v>54905500</v>
       </c>
       <c r="E17" s="3">
-        <v>21845000</v>
+        <v>21922300</v>
       </c>
       <c r="F17" s="3">
-        <v>19700300</v>
+        <v>19770000</v>
       </c>
       <c r="G17" s="3">
-        <v>20345500</v>
+        <v>20417500</v>
       </c>
       <c r="H17" s="3">
-        <v>21499500</v>
+        <v>21575500</v>
       </c>
       <c r="I17" s="3">
-        <v>19297400</v>
+        <v>19365600</v>
       </c>
       <c r="J17" s="3">
-        <v>-12729300</v>
+        <v>-12774300</v>
       </c>
       <c r="K17" s="3">
         <v>11880000</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-19923400</v>
+        <v>-19993900</v>
       </c>
       <c r="E18" s="3">
-        <v>13417900</v>
+        <v>13465300</v>
       </c>
       <c r="F18" s="3">
-        <v>13049400</v>
+        <v>13095500</v>
       </c>
       <c r="G18" s="3">
-        <v>12521500</v>
+        <v>12565800</v>
       </c>
       <c r="H18" s="3">
-        <v>11496300</v>
+        <v>11537000</v>
       </c>
       <c r="I18" s="3">
-        <v>11932400</v>
+        <v>11974600</v>
       </c>
       <c r="J18" s="3">
-        <v>37675400</v>
+        <v>37808600</v>
       </c>
       <c r="K18" s="3">
         <v>5649700</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>508800</v>
+        <v>510600</v>
       </c>
       <c r="E20" s="3">
-        <v>545700</v>
+        <v>547700</v>
       </c>
       <c r="F20" s="3">
-        <v>496000</v>
+        <v>497800</v>
       </c>
       <c r="G20" s="3">
-        <v>615900</v>
+        <v>618100</v>
       </c>
       <c r="H20" s="3">
-        <v>770200</v>
+        <v>772900</v>
       </c>
       <c r="I20" s="3">
-        <v>747200</v>
+        <v>749900</v>
       </c>
       <c r="J20" s="3">
-        <v>1352900</v>
+        <v>1357700</v>
       </c>
       <c r="K20" s="3">
         <v>2898000</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>17200100</v>
+        <v>16970900</v>
       </c>
       <c r="E21" s="3">
-        <v>15633500</v>
+        <v>15675600</v>
       </c>
       <c r="F21" s="3">
-        <v>14922200</v>
+        <v>14964100</v>
       </c>
       <c r="G21" s="3">
-        <v>14799600</v>
+        <v>14838700</v>
       </c>
       <c r="H21" s="3">
-        <v>14120600</v>
+        <v>14155900</v>
       </c>
       <c r="I21" s="3">
-        <v>13946400</v>
+        <v>13985700</v>
       </c>
       <c r="J21" s="3">
-        <v>40073700</v>
+        <v>40207200</v>
       </c>
       <c r="K21" s="3">
         <v>9301500</v>
@@ -1276,25 +1276,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2339800</v>
+        <v>2348100</v>
       </c>
       <c r="E22" s="3">
-        <v>2074600</v>
+        <v>2081900</v>
       </c>
       <c r="F22" s="3">
-        <v>1861600</v>
+        <v>1868200</v>
       </c>
       <c r="G22" s="3">
-        <v>2079700</v>
+        <v>2087000</v>
       </c>
       <c r="H22" s="3">
-        <v>2177900</v>
+        <v>2185600</v>
       </c>
       <c r="I22" s="3">
-        <v>2031200</v>
+        <v>2038400</v>
       </c>
       <c r="J22" s="3">
-        <v>1378400</v>
+        <v>1383300</v>
       </c>
       <c r="K22" s="3">
         <v>800200</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-21754500</v>
+        <v>-21831400</v>
       </c>
       <c r="E23" s="3">
-        <v>11889000</v>
+        <v>11931100</v>
       </c>
       <c r="F23" s="3">
-        <v>11683700</v>
+        <v>11725100</v>
       </c>
       <c r="G23" s="3">
-        <v>11057700</v>
+        <v>11096800</v>
       </c>
       <c r="H23" s="3">
-        <v>10088600</v>
+        <v>10124300</v>
       </c>
       <c r="I23" s="3">
-        <v>10648400</v>
+        <v>10686000</v>
       </c>
       <c r="J23" s="3">
-        <v>37649900</v>
+        <v>37783000</v>
       </c>
       <c r="K23" s="3">
         <v>7747500</v>
@@ -1366,25 +1366,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-3662100</v>
+        <v>-3675000</v>
       </c>
       <c r="E24" s="3">
-        <v>3159700</v>
+        <v>3170900</v>
       </c>
       <c r="F24" s="3">
-        <v>2992700</v>
+        <v>3003200</v>
       </c>
       <c r="G24" s="3">
-        <v>2857500</v>
+        <v>2867600</v>
       </c>
       <c r="H24" s="3">
-        <v>2690500</v>
+        <v>2700000</v>
       </c>
       <c r="I24" s="3">
-        <v>2819200</v>
+        <v>2829200</v>
       </c>
       <c r="J24" s="3">
-        <v>1857800</v>
+        <v>1864400</v>
       </c>
       <c r="K24" s="3">
         <v>1744300</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-18092400</v>
+        <v>-18156400</v>
       </c>
       <c r="E26" s="3">
-        <v>8729300</v>
+        <v>8760200</v>
       </c>
       <c r="F26" s="3">
-        <v>8691100</v>
+        <v>8721800</v>
       </c>
       <c r="G26" s="3">
-        <v>8200200</v>
+        <v>8229200</v>
       </c>
       <c r="H26" s="3">
-        <v>7398100</v>
+        <v>7424300</v>
       </c>
       <c r="I26" s="3">
-        <v>7829100</v>
+        <v>7856800</v>
       </c>
       <c r="J26" s="3">
-        <v>35792100</v>
+        <v>35918700</v>
       </c>
       <c r="K26" s="3">
         <v>6003300</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-18319400</v>
+        <v>-18384200</v>
       </c>
       <c r="E27" s="3">
-        <v>8499800</v>
+        <v>8529900</v>
       </c>
       <c r="F27" s="3">
-        <v>8470500</v>
+        <v>8500400</v>
       </c>
       <c r="G27" s="3">
-        <v>7991100</v>
+        <v>8019300</v>
       </c>
       <c r="H27" s="3">
-        <v>7213200</v>
+        <v>7238800</v>
       </c>
       <c r="I27" s="3">
-        <v>7602100</v>
+        <v>7629000</v>
       </c>
       <c r="J27" s="3">
-        <v>35574000</v>
+        <v>35699800</v>
       </c>
       <c r="K27" s="3">
         <v>5766300</v>
@@ -1597,19 +1597,19 @@
         <v>8</v>
       </c>
       <c r="F29" s="3">
-        <v>201500</v>
+        <v>202200</v>
       </c>
       <c r="G29" s="3">
-        <v>169600</v>
+        <v>170200</v>
       </c>
       <c r="H29" s="3">
-        <v>59900</v>
+        <v>60100</v>
       </c>
       <c r="I29" s="3">
-        <v>89300</v>
+        <v>89600</v>
       </c>
       <c r="J29" s="3">
-        <v>12223100</v>
+        <v>12266300</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-508800</v>
+        <v>-510600</v>
       </c>
       <c r="E32" s="3">
-        <v>-545700</v>
+        <v>-547700</v>
       </c>
       <c r="F32" s="3">
-        <v>-496000</v>
+        <v>-497800</v>
       </c>
       <c r="G32" s="3">
-        <v>-615900</v>
+        <v>-618100</v>
       </c>
       <c r="H32" s="3">
-        <v>-770200</v>
+        <v>-772900</v>
       </c>
       <c r="I32" s="3">
-        <v>-747200</v>
+        <v>-749900</v>
       </c>
       <c r="J32" s="3">
-        <v>-1352900</v>
+        <v>-1357700</v>
       </c>
       <c r="K32" s="3">
         <v>-2898000</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-18319400</v>
+        <v>-18384200</v>
       </c>
       <c r="E33" s="3">
-        <v>8499800</v>
+        <v>8529900</v>
       </c>
       <c r="F33" s="3">
-        <v>8672000</v>
+        <v>8702600</v>
       </c>
       <c r="G33" s="3">
-        <v>8160600</v>
+        <v>8189500</v>
       </c>
       <c r="H33" s="3">
-        <v>7273200</v>
+        <v>7298900</v>
       </c>
       <c r="I33" s="3">
-        <v>7691400</v>
+        <v>7718600</v>
       </c>
       <c r="J33" s="3">
-        <v>47797100</v>
+        <v>47966200</v>
       </c>
       <c r="K33" s="3">
         <v>5766300</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-18319400</v>
+        <v>-18384200</v>
       </c>
       <c r="E35" s="3">
-        <v>8499800</v>
+        <v>8529900</v>
       </c>
       <c r="F35" s="3">
-        <v>8672000</v>
+        <v>8702600</v>
       </c>
       <c r="G35" s="3">
-        <v>8160600</v>
+        <v>8189500</v>
       </c>
       <c r="H35" s="3">
-        <v>7273200</v>
+        <v>7298900</v>
       </c>
       <c r="I35" s="3">
-        <v>7691400</v>
+        <v>7718600</v>
       </c>
       <c r="J35" s="3">
-        <v>47797100</v>
+        <v>47966200</v>
       </c>
       <c r="K35" s="3">
         <v>5766300</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5940700</v>
+        <v>5961700</v>
       </c>
       <c r="E41" s="3">
-        <v>4394000</v>
+        <v>4409500</v>
       </c>
       <c r="F41" s="3">
-        <v>3581800</v>
+        <v>3594400</v>
       </c>
       <c r="G41" s="3">
-        <v>4002500</v>
+        <v>4016700</v>
       </c>
       <c r="H41" s="3">
-        <v>3220900</v>
+        <v>3232300</v>
       </c>
       <c r="I41" s="3">
-        <v>3317800</v>
+        <v>3329500</v>
       </c>
       <c r="J41" s="3">
-        <v>8392700</v>
+        <v>8422400</v>
       </c>
       <c r="K41" s="3">
         <v>2734300</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>766300</v>
+        <v>769000</v>
       </c>
       <c r="E42" s="3">
-        <v>738300</v>
+        <v>740900</v>
       </c>
       <c r="F42" s="3">
-        <v>581400</v>
+        <v>583500</v>
       </c>
       <c r="G42" s="3">
-        <v>308600</v>
+        <v>309700</v>
       </c>
       <c r="H42" s="3">
-        <v>156800</v>
+        <v>157400</v>
       </c>
       <c r="I42" s="3">
-        <v>227000</v>
+        <v>227800</v>
       </c>
       <c r="J42" s="3">
-        <v>82900</v>
+        <v>83200</v>
       </c>
       <c r="K42" s="3">
         <v>18600</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4836500</v>
+        <v>4853600</v>
       </c>
       <c r="E43" s="3">
-        <v>5758400</v>
+        <v>5778700</v>
       </c>
       <c r="F43" s="3">
-        <v>5187100</v>
+        <v>5205500</v>
       </c>
       <c r="G43" s="3">
-        <v>4845400</v>
+        <v>4862500</v>
       </c>
       <c r="H43" s="3">
-        <v>5374500</v>
+        <v>5393600</v>
       </c>
       <c r="I43" s="3">
-        <v>4669400</v>
+        <v>4685900</v>
       </c>
       <c r="J43" s="3">
-        <v>5754500</v>
+        <v>5774900</v>
       </c>
       <c r="K43" s="3">
         <v>4904100</v>
@@ -2129,25 +2129,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6296400</v>
+        <v>6318700</v>
       </c>
       <c r="E44" s="3">
-        <v>7231100</v>
+        <v>7256700</v>
       </c>
       <c r="F44" s="3">
-        <v>6731300</v>
+        <v>6755100</v>
       </c>
       <c r="G44" s="3">
-        <v>7648000</v>
+        <v>7675100</v>
       </c>
       <c r="H44" s="3">
-        <v>7770500</v>
+        <v>7797900</v>
       </c>
       <c r="I44" s="3">
-        <v>7687600</v>
+        <v>7714800</v>
       </c>
       <c r="J44" s="3">
-        <v>14954400</v>
+        <v>15007300</v>
       </c>
       <c r="K44" s="3">
         <v>7186800</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>248600</v>
+        <v>249500</v>
       </c>
       <c r="E45" s="3">
-        <v>1526300</v>
+        <v>1531700</v>
       </c>
       <c r="F45" s="3">
-        <v>248600</v>
+        <v>249500</v>
       </c>
       <c r="G45" s="3">
-        <v>552100</v>
+        <v>554100</v>
       </c>
       <c r="H45" s="3">
-        <v>402900</v>
+        <v>404400</v>
       </c>
       <c r="I45" s="3">
-        <v>234600</v>
+        <v>235400</v>
       </c>
       <c r="J45" s="3">
-        <v>297100</v>
+        <v>298100</v>
       </c>
       <c r="K45" s="3">
         <v>488800</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>18088600</v>
+        <v>18152500</v>
       </c>
       <c r="E46" s="3">
-        <v>19648000</v>
+        <v>19717500</v>
       </c>
       <c r="F46" s="3">
-        <v>16330200</v>
+        <v>16388000</v>
       </c>
       <c r="G46" s="3">
-        <v>17356700</v>
+        <v>17418100</v>
       </c>
       <c r="H46" s="3">
-        <v>16925700</v>
+        <v>16985500</v>
       </c>
       <c r="I46" s="3">
-        <v>16136400</v>
+        <v>16193500</v>
       </c>
       <c r="J46" s="3">
-        <v>17808000</v>
+        <v>17871000</v>
       </c>
       <c r="K46" s="3">
         <v>15332600</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3071700</v>
+        <v>3082600</v>
       </c>
       <c r="E47" s="3">
-        <v>3037300</v>
+        <v>3048000</v>
       </c>
       <c r="F47" s="3">
-        <v>2815400</v>
+        <v>2825400</v>
       </c>
       <c r="G47" s="3">
-        <v>2626700</v>
+        <v>2636000</v>
       </c>
       <c r="H47" s="3">
-        <v>2703200</v>
+        <v>2712800</v>
       </c>
       <c r="I47" s="3">
-        <v>3138000</v>
+        <v>3149100</v>
       </c>
       <c r="J47" s="3">
-        <v>3028400</v>
+        <v>3039100</v>
       </c>
       <c r="K47" s="3">
         <v>12590800</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5843800</v>
+        <v>5864500</v>
       </c>
       <c r="E48" s="3">
-        <v>6205900</v>
+        <v>6227900</v>
       </c>
       <c r="F48" s="3">
-        <v>6315600</v>
+        <v>6337900</v>
       </c>
       <c r="G48" s="3">
-        <v>6452000</v>
+        <v>6474800</v>
       </c>
       <c r="H48" s="3">
-        <v>7036000</v>
+        <v>7060900</v>
       </c>
       <c r="I48" s="3">
-        <v>6587200</v>
+        <v>6610500</v>
       </c>
       <c r="J48" s="3">
-        <v>12450100</v>
+        <v>12494100</v>
       </c>
       <c r="K48" s="3">
         <v>4541800</v>
@@ -2354,25 +2354,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>121851000</v>
+        <v>122282000</v>
       </c>
       <c r="E49" s="3">
-        <v>164584000</v>
+        <v>165166000</v>
       </c>
       <c r="F49" s="3">
-        <v>147433000</v>
+        <v>147955000</v>
       </c>
       <c r="G49" s="3">
-        <v>147074000</v>
+        <v>147594000</v>
       </c>
       <c r="H49" s="3">
-        <v>151465000</v>
+        <v>152001000</v>
       </c>
       <c r="I49" s="3">
-        <v>158129000</v>
+        <v>158688000</v>
       </c>
       <c r="J49" s="3">
-        <v>300375000</v>
+        <v>301438000</v>
       </c>
       <c r="K49" s="3">
         <v>15032400</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2519600</v>
+        <v>2528500</v>
       </c>
       <c r="E52" s="3">
-        <v>2311800</v>
+        <v>2319900</v>
       </c>
       <c r="F52" s="3">
-        <v>2259500</v>
+        <v>2267500</v>
       </c>
       <c r="G52" s="3">
-        <v>2059300</v>
+        <v>2066600</v>
       </c>
       <c r="H52" s="3">
-        <v>1665300</v>
+        <v>1671200</v>
       </c>
       <c r="I52" s="3">
-        <v>2610100</v>
+        <v>2619400</v>
       </c>
       <c r="J52" s="3">
-        <v>2608900</v>
+        <v>2618100</v>
       </c>
       <c r="K52" s="3">
         <v>1844800</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>151375000</v>
+        <v>151910000</v>
       </c>
       <c r="E54" s="3">
-        <v>195787000</v>
+        <v>196479000</v>
       </c>
       <c r="F54" s="3">
-        <v>175154000</v>
+        <v>175774000</v>
       </c>
       <c r="G54" s="3">
-        <v>175569000</v>
+        <v>176190000</v>
       </c>
       <c r="H54" s="3">
-        <v>179796000</v>
+        <v>180431000</v>
       </c>
       <c r="I54" s="3">
-        <v>186601000</v>
+        <v>187261000</v>
       </c>
       <c r="J54" s="3">
-        <v>179858000</v>
+        <v>180494000</v>
       </c>
       <c r="K54" s="3">
         <v>49342400</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>12368500</v>
+        <v>12412200</v>
       </c>
       <c r="E57" s="3">
-        <v>13323500</v>
+        <v>13370600</v>
       </c>
       <c r="F57" s="3">
-        <v>12211600</v>
+        <v>12254800</v>
       </c>
       <c r="G57" s="3">
-        <v>12359500</v>
+        <v>12403300</v>
       </c>
       <c r="H57" s="3">
-        <v>12402900</v>
+        <v>12446800</v>
       </c>
       <c r="I57" s="3">
-        <v>13555600</v>
+        <v>13603500</v>
       </c>
       <c r="J57" s="3">
-        <v>11358600</v>
+        <v>11398800</v>
       </c>
       <c r="K57" s="3">
         <v>9099800</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4782900</v>
+        <v>4799800</v>
       </c>
       <c r="E58" s="3">
-        <v>4958900</v>
+        <v>4976400</v>
       </c>
       <c r="F58" s="3">
-        <v>4503700</v>
+        <v>4519600</v>
       </c>
       <c r="G58" s="3">
-        <v>4516400</v>
+        <v>4532400</v>
       </c>
       <c r="H58" s="3">
-        <v>9037900</v>
+        <v>9069900</v>
       </c>
       <c r="I58" s="3">
-        <v>4788000</v>
+        <v>4804900</v>
       </c>
       <c r="J58" s="3">
-        <v>13262300</v>
+        <v>13309200</v>
       </c>
       <c r="K58" s="3">
         <v>3730500</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2833300</v>
+        <v>2843300</v>
       </c>
       <c r="E59" s="3">
-        <v>4482000</v>
+        <v>4497800</v>
       </c>
       <c r="F59" s="3">
-        <v>2594800</v>
+        <v>2604000</v>
       </c>
       <c r="G59" s="3">
-        <v>2860000</v>
+        <v>2870200</v>
       </c>
       <c r="H59" s="3">
-        <v>2560400</v>
+        <v>2569500</v>
       </c>
       <c r="I59" s="3">
-        <v>2477500</v>
+        <v>2486300</v>
       </c>
       <c r="J59" s="3">
-        <v>2700700</v>
+        <v>2710200</v>
       </c>
       <c r="K59" s="3">
         <v>1878300</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>19984600</v>
+        <v>20055300</v>
       </c>
       <c r="E60" s="3">
-        <v>22764400</v>
+        <v>22844900</v>
       </c>
       <c r="F60" s="3">
-        <v>19310100</v>
+        <v>19378400</v>
       </c>
       <c r="G60" s="3">
-        <v>19736000</v>
+        <v>19805800</v>
       </c>
       <c r="H60" s="3">
-        <v>24001200</v>
+        <v>24086100</v>
       </c>
       <c r="I60" s="3">
-        <v>20821100</v>
+        <v>20894800</v>
       </c>
       <c r="J60" s="3">
-        <v>19897900</v>
+        <v>19968300</v>
       </c>
       <c r="K60" s="3">
         <v>14708600</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>45146200</v>
+        <v>45305900</v>
       </c>
       <c r="E61" s="3">
-        <v>49379500</v>
+        <v>49554200</v>
       </c>
       <c r="F61" s="3">
-        <v>45477700</v>
+        <v>45638600</v>
       </c>
       <c r="G61" s="3">
-        <v>50910900</v>
+        <v>51091000</v>
       </c>
       <c r="H61" s="3">
-        <v>48203900</v>
+        <v>48374400</v>
       </c>
       <c r="I61" s="3">
-        <v>55191400</v>
+        <v>55386600</v>
       </c>
       <c r="J61" s="3">
-        <v>56138800</v>
+        <v>56337400</v>
       </c>
       <c r="K61" s="3">
         <v>20455000</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>18747800</v>
+        <v>18814100</v>
       </c>
       <c r="E62" s="3">
-        <v>27104800</v>
+        <v>27200700</v>
       </c>
       <c r="F62" s="3">
-        <v>24423300</v>
+        <v>24509600</v>
       </c>
       <c r="G62" s="3">
-        <v>24647700</v>
+        <v>24734900</v>
       </c>
       <c r="H62" s="3">
-        <v>25780000</v>
+        <v>25871200</v>
       </c>
       <c r="I62" s="3">
-        <v>26829400</v>
+        <v>26924300</v>
       </c>
       <c r="J62" s="3">
-        <v>26515700</v>
+        <v>26609500</v>
       </c>
       <c r="K62" s="3">
         <v>3750300</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>84347900</v>
+        <v>84646200</v>
       </c>
       <c r="E66" s="3">
-        <v>99684800</v>
+        <v>100037000</v>
       </c>
       <c r="F66" s="3">
-        <v>89593600</v>
+        <v>89910500</v>
       </c>
       <c r="G66" s="3">
-        <v>95654200</v>
+        <v>95992500</v>
       </c>
       <c r="H66" s="3">
-        <v>98314000</v>
+        <v>98661800</v>
       </c>
       <c r="I66" s="3">
-        <v>103153000</v>
+        <v>103518000</v>
       </c>
       <c r="J66" s="3">
-        <v>102384000</v>
+        <v>102746000</v>
       </c>
       <c r="K66" s="3">
         <v>39191800</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>74867500</v>
+        <v>75132300</v>
       </c>
       <c r="E72" s="3">
-        <v>99821200</v>
+        <v>100174000</v>
       </c>
       <c r="F72" s="3">
-        <v>97445700</v>
+        <v>97790400</v>
       </c>
       <c r="G72" s="3">
-        <v>94713200</v>
+        <v>95048200</v>
       </c>
       <c r="H72" s="3">
-        <v>92550600</v>
+        <v>92877900</v>
       </c>
       <c r="I72" s="3">
-        <v>90388000</v>
+        <v>90707700</v>
       </c>
       <c r="J72" s="3">
-        <v>131031000</v>
+        <v>131494000</v>
       </c>
       <c r="K72" s="3">
         <v>9419900</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>67026900</v>
+        <v>67264000</v>
       </c>
       <c r="E76" s="3">
-        <v>96101700</v>
+        <v>96441600</v>
       </c>
       <c r="F76" s="3">
-        <v>85560500</v>
+        <v>85863100</v>
       </c>
       <c r="G76" s="3">
-        <v>79914300</v>
+        <v>80197000</v>
       </c>
       <c r="H76" s="3">
-        <v>81481400</v>
+        <v>81769600</v>
       </c>
       <c r="I76" s="3">
-        <v>83447600</v>
+        <v>83742800</v>
       </c>
       <c r="J76" s="3">
-        <v>77473800</v>
+        <v>77747800</v>
       </c>
       <c r="K76" s="3">
         <v>10150600</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-18319400</v>
+        <v>-18384200</v>
       </c>
       <c r="E81" s="3">
-        <v>8499800</v>
+        <v>8529900</v>
       </c>
       <c r="F81" s="3">
-        <v>8672000</v>
+        <v>8702600</v>
       </c>
       <c r="G81" s="3">
-        <v>8160600</v>
+        <v>8189500</v>
       </c>
       <c r="H81" s="3">
-        <v>7273200</v>
+        <v>7298900</v>
       </c>
       <c r="I81" s="3">
-        <v>7691400</v>
+        <v>7718600</v>
       </c>
       <c r="J81" s="3">
-        <v>47797100</v>
+        <v>47966200</v>
       </c>
       <c r="K81" s="3">
         <v>5766300</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>36485700</v>
+        <v>36614800</v>
       </c>
       <c r="E83" s="3">
-        <v>1664000</v>
+        <v>1669900</v>
       </c>
       <c r="F83" s="3">
-        <v>1372000</v>
+        <v>1376900</v>
       </c>
       <c r="G83" s="3">
-        <v>1656400</v>
+        <v>1662200</v>
       </c>
       <c r="H83" s="3">
-        <v>1847600</v>
+        <v>1854200</v>
       </c>
       <c r="I83" s="3">
-        <v>1262300</v>
+        <v>1266800</v>
       </c>
       <c r="J83" s="3">
-        <v>1041800</v>
+        <v>1045400</v>
       </c>
       <c r="K83" s="3">
         <v>753000</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>14130700</v>
+        <v>14180600</v>
       </c>
       <c r="E89" s="3">
-        <v>12784200</v>
+        <v>12829400</v>
       </c>
       <c r="F89" s="3">
-        <v>12390100</v>
+        <v>12434000</v>
       </c>
       <c r="G89" s="3">
-        <v>12478100</v>
+        <v>12522300</v>
       </c>
       <c r="H89" s="3">
-        <v>11470800</v>
+        <v>11511400</v>
       </c>
       <c r="I89" s="3">
-        <v>13127200</v>
+        <v>13173600</v>
       </c>
       <c r="J89" s="3">
-        <v>6818000</v>
+        <v>6842100</v>
       </c>
       <c r="K89" s="3">
         <v>5719200</v>
@@ -4029,25 +4029,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-586500</v>
+        <v>-588600</v>
       </c>
       <c r="E91" s="3">
-        <v>-666900</v>
+        <v>-669200</v>
       </c>
       <c r="F91" s="3">
-        <v>-672000</v>
+        <v>-674400</v>
       </c>
       <c r="G91" s="3">
-        <v>-651600</v>
+        <v>-653900</v>
       </c>
       <c r="H91" s="3">
-        <v>-846700</v>
+        <v>-849700</v>
       </c>
       <c r="I91" s="3">
-        <v>-966500</v>
+        <v>-969900</v>
       </c>
       <c r="J91" s="3">
-        <v>-1008600</v>
+        <v>-1012200</v>
       </c>
       <c r="K91" s="3">
         <v>-727000</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-377400</v>
+        <v>-378800</v>
       </c>
       <c r="E94" s="3">
-        <v>-898900</v>
+        <v>-902100</v>
       </c>
       <c r="F94" s="3">
-        <v>-1453600</v>
+        <v>-1458800</v>
       </c>
       <c r="G94" s="3">
-        <v>-998400</v>
+        <v>-1001900</v>
       </c>
       <c r="H94" s="3">
-        <v>-814800</v>
+        <v>-817700</v>
       </c>
       <c r="I94" s="3">
-        <v>-1301900</v>
+        <v>-1306500</v>
       </c>
       <c r="J94" s="3">
-        <v>-23645500</v>
+        <v>-23729100</v>
       </c>
       <c r="K94" s="3">
         <v>-794000</v>
@@ -4228,25 +4228,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-6445600</v>
+        <v>-6468400</v>
       </c>
       <c r="E96" s="3">
-        <v>-6267100</v>
+        <v>-6289300</v>
       </c>
       <c r="F96" s="3">
-        <v>-6253100</v>
+        <v>-6275200</v>
       </c>
       <c r="G96" s="3">
-        <v>-6050300</v>
+        <v>-6071700</v>
       </c>
       <c r="H96" s="3">
-        <v>-5862900</v>
+        <v>-5883600</v>
       </c>
       <c r="I96" s="3">
-        <v>-5542900</v>
+        <v>-5562500</v>
       </c>
       <c r="J96" s="3">
-        <v>-4418200</v>
+        <v>-4433800</v>
       </c>
       <c r="K96" s="3">
         <v>-3610100</v>
@@ -4408,25 +4408,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-11876300</v>
+        <v>-11918300</v>
       </c>
       <c r="E100" s="3">
-        <v>-11320300</v>
+        <v>-11360400</v>
       </c>
       <c r="F100" s="3">
-        <v>-11155800</v>
+        <v>-11195300</v>
       </c>
       <c r="G100" s="3">
-        <v>-10069500</v>
+        <v>-10105100</v>
       </c>
       <c r="H100" s="3">
-        <v>-10956900</v>
+        <v>-10995700</v>
       </c>
       <c r="I100" s="3">
-        <v>-12279200</v>
+        <v>-12322600</v>
       </c>
       <c r="J100" s="3">
-        <v>18819200</v>
+        <v>18885800</v>
       </c>
       <c r="K100" s="3">
         <v>-5246500</v>
@@ -4453,25 +4453,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-372300</v>
+        <v>-373600</v>
       </c>
       <c r="E101" s="3">
-        <v>549600</v>
+        <v>551500</v>
       </c>
       <c r="F101" s="3">
-        <v>-322600</v>
+        <v>-323700</v>
       </c>
       <c r="G101" s="3">
-        <v>-322600</v>
+        <v>-323700</v>
       </c>
       <c r="H101" s="3">
-        <v>-72700</v>
+        <v>-72900</v>
       </c>
       <c r="I101" s="3">
-        <v>-176000</v>
+        <v>-176600</v>
       </c>
       <c r="J101" s="3">
-        <v>-498600</v>
+        <v>-500300</v>
       </c>
       <c r="K101" s="3">
         <v>223300</v>
@@ -4498,25 +4498,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1973900</v>
+        <v>1509900</v>
       </c>
       <c r="E102" s="3">
-        <v>1114400</v>
+        <v>1118400</v>
       </c>
       <c r="F102" s="3">
-        <v>-541900</v>
+        <v>-543800</v>
       </c>
       <c r="G102" s="3">
-        <v>1087700</v>
+        <v>1091500</v>
       </c>
       <c r="H102" s="3">
-        <v>-373600</v>
+        <v>-374900</v>
       </c>
       <c r="I102" s="3">
-        <v>-629900</v>
+        <v>-632100</v>
       </c>
       <c r="J102" s="3">
-        <v>1493100</v>
+        <v>1498400</v>
       </c>
       <c r="K102" s="3">
         <v>-98000</v>

--- a/AAII_Financials/Yearly/BTI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BTI_YR_FIN.xlsx
@@ -727,25 +727,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>34911600</v>
+        <v>35800800</v>
       </c>
       <c r="E8" s="3">
-        <v>35387600</v>
+        <v>36288900</v>
       </c>
       <c r="F8" s="3">
-        <v>32865500</v>
+        <v>33702500</v>
       </c>
       <c r="G8" s="3">
-        <v>32983200</v>
+        <v>33823300</v>
       </c>
       <c r="H8" s="3">
-        <v>33112500</v>
+        <v>33955800</v>
       </c>
       <c r="I8" s="3">
-        <v>31340200</v>
+        <v>32138400</v>
       </c>
       <c r="J8" s="3">
-        <v>25034300</v>
+        <v>25671900</v>
       </c>
       <c r="K8" s="3">
         <v>17529700</v>
@@ -772,25 +772,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6258600</v>
+        <v>6418000</v>
       </c>
       <c r="E9" s="3">
-        <v>6147200</v>
+        <v>6303800</v>
       </c>
       <c r="F9" s="3">
-        <v>5882400</v>
+        <v>6032200</v>
       </c>
       <c r="G9" s="3">
-        <v>5295000</v>
+        <v>5429900</v>
       </c>
       <c r="H9" s="3">
-        <v>5677600</v>
+        <v>5822200</v>
       </c>
       <c r="I9" s="3">
-        <v>5822200</v>
+        <v>5970500</v>
       </c>
       <c r="J9" s="3">
-        <v>6440300</v>
+        <v>6604300</v>
       </c>
       <c r="K9" s="3">
         <v>4631200</v>
@@ -817,25 +817,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>28653000</v>
+        <v>29382800</v>
       </c>
       <c r="E10" s="3">
-        <v>29240400</v>
+        <v>29985100</v>
       </c>
       <c r="F10" s="3">
-        <v>26983100</v>
+        <v>27670400</v>
       </c>
       <c r="G10" s="3">
-        <v>27688200</v>
+        <v>28393400</v>
       </c>
       <c r="H10" s="3">
-        <v>27434800</v>
+        <v>28133600</v>
       </c>
       <c r="I10" s="3">
-        <v>25518000</v>
+        <v>26167900</v>
       </c>
       <c r="J10" s="3">
-        <v>18594000</v>
+        <v>19067600</v>
       </c>
       <c r="K10" s="3">
         <v>12898500</v>
@@ -881,25 +881,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>231600</v>
+        <v>237500</v>
       </c>
       <c r="E12" s="3">
-        <v>176600</v>
+        <v>181100</v>
       </c>
       <c r="F12" s="3">
-        <v>180400</v>
+        <v>185000</v>
       </c>
       <c r="G12" s="3">
-        <v>154800</v>
+        <v>158800</v>
       </c>
       <c r="H12" s="3">
-        <v>161200</v>
+        <v>165300</v>
       </c>
       <c r="I12" s="3">
-        <v>134400</v>
+        <v>137800</v>
       </c>
       <c r="J12" s="3">
-        <v>102400</v>
+        <v>105000</v>
       </c>
       <c r="K12" s="3">
         <v>65800</v>
@@ -971,25 +971,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>36129800</v>
+        <v>37050000</v>
       </c>
       <c r="E14" s="3">
-        <v>1041600</v>
+        <v>1068100</v>
       </c>
       <c r="F14" s="3">
-        <v>830500</v>
+        <v>851600</v>
       </c>
       <c r="G14" s="3">
-        <v>975100</v>
+        <v>999900</v>
       </c>
       <c r="H14" s="3">
-        <v>975100</v>
+        <v>999900</v>
       </c>
       <c r="I14" s="3">
-        <v>410800</v>
+        <v>421200</v>
       </c>
       <c r="J14" s="3">
-        <v>-28836000</v>
+        <v>-29570400</v>
       </c>
       <c r="K14" s="3">
         <v>873400</v>
@@ -1016,25 +1016,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1104300</v>
+        <v>1132400</v>
       </c>
       <c r="E15" s="3">
-        <v>1248900</v>
+        <v>1280700</v>
       </c>
       <c r="F15" s="3">
-        <v>1214300</v>
+        <v>1245300</v>
       </c>
       <c r="G15" s="3">
-        <v>1394800</v>
+        <v>1430300</v>
       </c>
       <c r="H15" s="3">
-        <v>1605900</v>
+        <v>1646800</v>
       </c>
       <c r="I15" s="3">
-        <v>1266800</v>
+        <v>1299100</v>
       </c>
       <c r="J15" s="3">
-        <v>1045400</v>
+        <v>1072100</v>
       </c>
       <c r="K15" s="3">
         <v>1346100</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>54905500</v>
+        <v>56303900</v>
       </c>
       <c r="E17" s="3">
-        <v>21922300</v>
+        <v>22480600</v>
       </c>
       <c r="F17" s="3">
-        <v>19770000</v>
+        <v>20273500</v>
       </c>
       <c r="G17" s="3">
-        <v>20417500</v>
+        <v>20937500</v>
       </c>
       <c r="H17" s="3">
-        <v>21575500</v>
+        <v>22125000</v>
       </c>
       <c r="I17" s="3">
-        <v>19365600</v>
+        <v>19858800</v>
       </c>
       <c r="J17" s="3">
-        <v>-12774300</v>
+        <v>-13099700</v>
       </c>
       <c r="K17" s="3">
         <v>11880000</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-19993900</v>
+        <v>-20503100</v>
       </c>
       <c r="E18" s="3">
-        <v>13465300</v>
+        <v>13808300</v>
       </c>
       <c r="F18" s="3">
-        <v>13095500</v>
+        <v>13429100</v>
       </c>
       <c r="G18" s="3">
-        <v>12565800</v>
+        <v>12885800</v>
       </c>
       <c r="H18" s="3">
-        <v>11537000</v>
+        <v>11830800</v>
       </c>
       <c r="I18" s="3">
-        <v>11974600</v>
+        <v>12279600</v>
       </c>
       <c r="J18" s="3">
-        <v>37808600</v>
+        <v>38771600</v>
       </c>
       <c r="K18" s="3">
         <v>5649700</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>510600</v>
+        <v>523600</v>
       </c>
       <c r="E20" s="3">
-        <v>547700</v>
+        <v>561600</v>
       </c>
       <c r="F20" s="3">
-        <v>497800</v>
+        <v>510400</v>
       </c>
       <c r="G20" s="3">
-        <v>618100</v>
+        <v>633800</v>
       </c>
       <c r="H20" s="3">
-        <v>772900</v>
+        <v>792600</v>
       </c>
       <c r="I20" s="3">
-        <v>749900</v>
+        <v>768900</v>
       </c>
       <c r="J20" s="3">
-        <v>1357700</v>
+        <v>1392200</v>
       </c>
       <c r="K20" s="3">
         <v>2898000</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>16970900</v>
+        <v>17570600</v>
       </c>
       <c r="E21" s="3">
-        <v>15675600</v>
+        <v>16082500</v>
       </c>
       <c r="F21" s="3">
-        <v>14964100</v>
+        <v>15351500</v>
       </c>
       <c r="G21" s="3">
-        <v>14838700</v>
+        <v>15224300</v>
       </c>
       <c r="H21" s="3">
-        <v>14155900</v>
+        <v>14524900</v>
       </c>
       <c r="I21" s="3">
-        <v>13985700</v>
+        <v>14347700</v>
       </c>
       <c r="J21" s="3">
-        <v>40207200</v>
+        <v>41236000</v>
       </c>
       <c r="K21" s="3">
         <v>9301500</v>
@@ -1276,25 +1276,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2348100</v>
+        <v>2407900</v>
       </c>
       <c r="E22" s="3">
-        <v>2081900</v>
+        <v>2134900</v>
       </c>
       <c r="F22" s="3">
-        <v>1868200</v>
+        <v>1915800</v>
       </c>
       <c r="G22" s="3">
-        <v>2087000</v>
+        <v>2140200</v>
       </c>
       <c r="H22" s="3">
-        <v>2185600</v>
+        <v>2241200</v>
       </c>
       <c r="I22" s="3">
-        <v>2038400</v>
+        <v>2090300</v>
       </c>
       <c r="J22" s="3">
-        <v>1383300</v>
+        <v>1418500</v>
       </c>
       <c r="K22" s="3">
         <v>800200</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-21831400</v>
+        <v>-22387400</v>
       </c>
       <c r="E23" s="3">
-        <v>11931100</v>
+        <v>12235000</v>
       </c>
       <c r="F23" s="3">
-        <v>11725100</v>
+        <v>12023700</v>
       </c>
       <c r="G23" s="3">
-        <v>11096800</v>
+        <v>11379400</v>
       </c>
       <c r="H23" s="3">
-        <v>10124300</v>
+        <v>10382100</v>
       </c>
       <c r="I23" s="3">
-        <v>10686000</v>
+        <v>10958200</v>
       </c>
       <c r="J23" s="3">
-        <v>37783000</v>
+        <v>38745300</v>
       </c>
       <c r="K23" s="3">
         <v>7747500</v>
@@ -1366,25 +1366,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-3675000</v>
+        <v>-3768600</v>
       </c>
       <c r="E24" s="3">
-        <v>3170900</v>
+        <v>3251600</v>
       </c>
       <c r="F24" s="3">
-        <v>3003200</v>
+        <v>3079700</v>
       </c>
       <c r="G24" s="3">
-        <v>2867600</v>
+        <v>2940600</v>
       </c>
       <c r="H24" s="3">
-        <v>2700000</v>
+        <v>2768700</v>
       </c>
       <c r="I24" s="3">
-        <v>2829200</v>
+        <v>2901300</v>
       </c>
       <c r="J24" s="3">
-        <v>1864400</v>
+        <v>1911900</v>
       </c>
       <c r="K24" s="3">
         <v>1744300</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-18156400</v>
+        <v>-18618800</v>
       </c>
       <c r="E26" s="3">
-        <v>8760200</v>
+        <v>8983300</v>
       </c>
       <c r="F26" s="3">
-        <v>8721800</v>
+        <v>8944000</v>
       </c>
       <c r="G26" s="3">
-        <v>8229200</v>
+        <v>8438800</v>
       </c>
       <c r="H26" s="3">
-        <v>7424300</v>
+        <v>7613400</v>
       </c>
       <c r="I26" s="3">
-        <v>7856800</v>
+        <v>8056900</v>
       </c>
       <c r="J26" s="3">
-        <v>35918700</v>
+        <v>36833500</v>
       </c>
       <c r="K26" s="3">
         <v>6003300</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-18384200</v>
+        <v>-18852400</v>
       </c>
       <c r="E27" s="3">
-        <v>8529900</v>
+        <v>8747100</v>
       </c>
       <c r="F27" s="3">
-        <v>8500400</v>
+        <v>8716900</v>
       </c>
       <c r="G27" s="3">
-        <v>8019300</v>
+        <v>8223600</v>
       </c>
       <c r="H27" s="3">
-        <v>7238800</v>
+        <v>7423100</v>
       </c>
       <c r="I27" s="3">
-        <v>7629000</v>
+        <v>7823300</v>
       </c>
       <c r="J27" s="3">
-        <v>35699800</v>
+        <v>36609100</v>
       </c>
       <c r="K27" s="3">
         <v>5766300</v>
@@ -1597,19 +1597,19 @@
         <v>8</v>
       </c>
       <c r="F29" s="3">
-        <v>202200</v>
+        <v>207300</v>
       </c>
       <c r="G29" s="3">
-        <v>170200</v>
+        <v>174500</v>
       </c>
       <c r="H29" s="3">
-        <v>60100</v>
+        <v>61700</v>
       </c>
       <c r="I29" s="3">
-        <v>89600</v>
+        <v>91900</v>
       </c>
       <c r="J29" s="3">
-        <v>12266300</v>
+        <v>12578700</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-510600</v>
+        <v>-523600</v>
       </c>
       <c r="E32" s="3">
-        <v>-547700</v>
+        <v>-561600</v>
       </c>
       <c r="F32" s="3">
-        <v>-497800</v>
+        <v>-510400</v>
       </c>
       <c r="G32" s="3">
-        <v>-618100</v>
+        <v>-633800</v>
       </c>
       <c r="H32" s="3">
-        <v>-772900</v>
+        <v>-792600</v>
       </c>
       <c r="I32" s="3">
-        <v>-749900</v>
+        <v>-768900</v>
       </c>
       <c r="J32" s="3">
-        <v>-1357700</v>
+        <v>-1392200</v>
       </c>
       <c r="K32" s="3">
         <v>-2898000</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-18384200</v>
+        <v>-18852400</v>
       </c>
       <c r="E33" s="3">
-        <v>8529900</v>
+        <v>8747100</v>
       </c>
       <c r="F33" s="3">
-        <v>8702600</v>
+        <v>8924300</v>
       </c>
       <c r="G33" s="3">
-        <v>8189500</v>
+        <v>8398100</v>
       </c>
       <c r="H33" s="3">
-        <v>7298900</v>
+        <v>7484800</v>
       </c>
       <c r="I33" s="3">
-        <v>7718600</v>
+        <v>7915200</v>
       </c>
       <c r="J33" s="3">
-        <v>47966200</v>
+        <v>49187800</v>
       </c>
       <c r="K33" s="3">
         <v>5766300</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-18384200</v>
+        <v>-18852400</v>
       </c>
       <c r="E35" s="3">
-        <v>8529900</v>
+        <v>8747100</v>
       </c>
       <c r="F35" s="3">
-        <v>8702600</v>
+        <v>8924300</v>
       </c>
       <c r="G35" s="3">
-        <v>8189500</v>
+        <v>8398100</v>
       </c>
       <c r="H35" s="3">
-        <v>7298900</v>
+        <v>7484800</v>
       </c>
       <c r="I35" s="3">
-        <v>7718600</v>
+        <v>7915200</v>
       </c>
       <c r="J35" s="3">
-        <v>47966200</v>
+        <v>49187800</v>
       </c>
       <c r="K35" s="3">
         <v>5766300</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5961700</v>
+        <v>6113500</v>
       </c>
       <c r="E41" s="3">
-        <v>4409500</v>
+        <v>4521800</v>
       </c>
       <c r="F41" s="3">
-        <v>3594400</v>
+        <v>3686000</v>
       </c>
       <c r="G41" s="3">
-        <v>4016700</v>
+        <v>4119000</v>
       </c>
       <c r="H41" s="3">
-        <v>3232300</v>
+        <v>3314600</v>
       </c>
       <c r="I41" s="3">
-        <v>3329500</v>
+        <v>3414300</v>
       </c>
       <c r="J41" s="3">
-        <v>8422400</v>
+        <v>8636900</v>
       </c>
       <c r="K41" s="3">
         <v>2734300</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>769000</v>
+        <v>788600</v>
       </c>
       <c r="E42" s="3">
-        <v>740900</v>
+        <v>759800</v>
       </c>
       <c r="F42" s="3">
-        <v>583500</v>
+        <v>598400</v>
       </c>
       <c r="G42" s="3">
-        <v>309700</v>
+        <v>317600</v>
       </c>
       <c r="H42" s="3">
-        <v>157400</v>
+        <v>161400</v>
       </c>
       <c r="I42" s="3">
-        <v>227800</v>
+        <v>233600</v>
       </c>
       <c r="J42" s="3">
-        <v>83200</v>
+        <v>85300</v>
       </c>
       <c r="K42" s="3">
         <v>18600</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4853600</v>
+        <v>4977200</v>
       </c>
       <c r="E43" s="3">
-        <v>5778700</v>
+        <v>5925900</v>
       </c>
       <c r="F43" s="3">
-        <v>5205500</v>
+        <v>5338000</v>
       </c>
       <c r="G43" s="3">
-        <v>4862500</v>
+        <v>4986400</v>
       </c>
       <c r="H43" s="3">
-        <v>5393600</v>
+        <v>5530900</v>
       </c>
       <c r="I43" s="3">
-        <v>4685900</v>
+        <v>4805300</v>
       </c>
       <c r="J43" s="3">
-        <v>5774900</v>
+        <v>5922000</v>
       </c>
       <c r="K43" s="3">
         <v>4904100</v>
@@ -2129,25 +2129,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6318700</v>
+        <v>6479600</v>
       </c>
       <c r="E44" s="3">
-        <v>7256700</v>
+        <v>7441500</v>
       </c>
       <c r="F44" s="3">
-        <v>6755100</v>
+        <v>6927100</v>
       </c>
       <c r="G44" s="3">
-        <v>7675100</v>
+        <v>7870600</v>
       </c>
       <c r="H44" s="3">
-        <v>7797900</v>
+        <v>7996500</v>
       </c>
       <c r="I44" s="3">
-        <v>7714800</v>
+        <v>7911300</v>
       </c>
       <c r="J44" s="3">
-        <v>15007300</v>
+        <v>15389500</v>
       </c>
       <c r="K44" s="3">
         <v>7186800</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>249500</v>
+        <v>255900</v>
       </c>
       <c r="E45" s="3">
-        <v>1531700</v>
+        <v>1570700</v>
       </c>
       <c r="F45" s="3">
-        <v>249500</v>
+        <v>255900</v>
       </c>
       <c r="G45" s="3">
-        <v>554100</v>
+        <v>568200</v>
       </c>
       <c r="H45" s="3">
-        <v>404400</v>
+        <v>414700</v>
       </c>
       <c r="I45" s="3">
-        <v>235400</v>
+        <v>241400</v>
       </c>
       <c r="J45" s="3">
-        <v>298100</v>
+        <v>305700</v>
       </c>
       <c r="K45" s="3">
         <v>488800</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>18152500</v>
+        <v>18614900</v>
       </c>
       <c r="E46" s="3">
-        <v>19717500</v>
+        <v>20219700</v>
       </c>
       <c r="F46" s="3">
-        <v>16388000</v>
+        <v>16805300</v>
       </c>
       <c r="G46" s="3">
+        <v>17861700</v>
+      </c>
+      <c r="H46" s="3">
         <v>17418100</v>
       </c>
-      <c r="H46" s="3">
-        <v>16985500</v>
-      </c>
       <c r="I46" s="3">
-        <v>16193500</v>
+        <v>16605900</v>
       </c>
       <c r="J46" s="3">
-        <v>17871000</v>
+        <v>18326200</v>
       </c>
       <c r="K46" s="3">
         <v>15332600</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3082600</v>
+        <v>3161100</v>
       </c>
       <c r="E47" s="3">
-        <v>3048000</v>
+        <v>3125700</v>
       </c>
       <c r="F47" s="3">
-        <v>2825400</v>
+        <v>2897300</v>
       </c>
       <c r="G47" s="3">
-        <v>2636000</v>
+        <v>2703100</v>
       </c>
       <c r="H47" s="3">
-        <v>2712800</v>
+        <v>2781900</v>
       </c>
       <c r="I47" s="3">
-        <v>3149100</v>
+        <v>3229300</v>
       </c>
       <c r="J47" s="3">
-        <v>3039100</v>
+        <v>3116500</v>
       </c>
       <c r="K47" s="3">
         <v>12590800</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5864500</v>
+        <v>6013800</v>
       </c>
       <c r="E48" s="3">
-        <v>6227900</v>
+        <v>6386500</v>
       </c>
       <c r="F48" s="3">
-        <v>6337900</v>
+        <v>6499300</v>
       </c>
       <c r="G48" s="3">
-        <v>6474800</v>
+        <v>6639700</v>
       </c>
       <c r="H48" s="3">
-        <v>7060900</v>
+        <v>7240700</v>
       </c>
       <c r="I48" s="3">
-        <v>6610500</v>
+        <v>6778800</v>
       </c>
       <c r="J48" s="3">
-        <v>12494100</v>
+        <v>12812300</v>
       </c>
       <c r="K48" s="3">
         <v>4541800</v>
@@ -2354,25 +2354,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>122282000</v>
+        <v>125397000</v>
       </c>
       <c r="E49" s="3">
-        <v>165166000</v>
+        <v>169372000</v>
       </c>
       <c r="F49" s="3">
-        <v>147955000</v>
+        <v>151723000</v>
       </c>
       <c r="G49" s="3">
-        <v>147594000</v>
+        <v>151353000</v>
       </c>
       <c r="H49" s="3">
-        <v>152001000</v>
+        <v>155872000</v>
       </c>
       <c r="I49" s="3">
-        <v>158688000</v>
+        <v>162730000</v>
       </c>
       <c r="J49" s="3">
-        <v>301438000</v>
+        <v>309115000</v>
       </c>
       <c r="K49" s="3">
         <v>15032400</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2528500</v>
+        <v>2592900</v>
       </c>
       <c r="E52" s="3">
-        <v>2319900</v>
+        <v>2379000</v>
       </c>
       <c r="F52" s="3">
-        <v>2267500</v>
+        <v>2325200</v>
       </c>
       <c r="G52" s="3">
-        <v>2066600</v>
+        <v>2119200</v>
       </c>
       <c r="H52" s="3">
-        <v>1671200</v>
+        <v>1713700</v>
       </c>
       <c r="I52" s="3">
-        <v>2619400</v>
+        <v>2686100</v>
       </c>
       <c r="J52" s="3">
-        <v>2618100</v>
+        <v>2684800</v>
       </c>
       <c r="K52" s="3">
         <v>1844800</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>151910000</v>
+        <v>155779000</v>
       </c>
       <c r="E54" s="3">
-        <v>196479000</v>
+        <v>201483000</v>
       </c>
       <c r="F54" s="3">
-        <v>175774000</v>
+        <v>180250000</v>
       </c>
       <c r="G54" s="3">
-        <v>176190000</v>
+        <v>180677000</v>
       </c>
       <c r="H54" s="3">
-        <v>180431000</v>
+        <v>185027000</v>
       </c>
       <c r="I54" s="3">
-        <v>187261000</v>
+        <v>192030000</v>
       </c>
       <c r="J54" s="3">
-        <v>180494000</v>
+        <v>185091000</v>
       </c>
       <c r="K54" s="3">
         <v>49342400</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>12412200</v>
+        <v>12728300</v>
       </c>
       <c r="E57" s="3">
-        <v>13370600</v>
+        <v>13711200</v>
       </c>
       <c r="F57" s="3">
-        <v>12254800</v>
+        <v>12566900</v>
       </c>
       <c r="G57" s="3">
-        <v>12403300</v>
+        <v>12719200</v>
       </c>
       <c r="H57" s="3">
-        <v>12446800</v>
+        <v>12763800</v>
       </c>
       <c r="I57" s="3">
-        <v>13603500</v>
+        <v>13950000</v>
       </c>
       <c r="J57" s="3">
-        <v>11398800</v>
+        <v>11689100</v>
       </c>
       <c r="K57" s="3">
         <v>9099800</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4799800</v>
+        <v>4922100</v>
       </c>
       <c r="E58" s="3">
-        <v>4976400</v>
+        <v>5103100</v>
       </c>
       <c r="F58" s="3">
-        <v>4519600</v>
+        <v>4634700</v>
       </c>
       <c r="G58" s="3">
-        <v>4532400</v>
+        <v>4647800</v>
       </c>
       <c r="H58" s="3">
-        <v>9069900</v>
+        <v>9300900</v>
       </c>
       <c r="I58" s="3">
-        <v>4804900</v>
+        <v>4927300</v>
       </c>
       <c r="J58" s="3">
-        <v>13309200</v>
+        <v>13648200</v>
       </c>
       <c r="K58" s="3">
         <v>3730500</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2843300</v>
+        <v>2915700</v>
       </c>
       <c r="E59" s="3">
-        <v>4497800</v>
+        <v>4612400</v>
       </c>
       <c r="F59" s="3">
-        <v>2604000</v>
+        <v>2670300</v>
       </c>
       <c r="G59" s="3">
-        <v>2870200</v>
+        <v>2943300</v>
       </c>
       <c r="H59" s="3">
-        <v>2569500</v>
+        <v>2634900</v>
       </c>
       <c r="I59" s="3">
-        <v>2486300</v>
+        <v>2549600</v>
       </c>
       <c r="J59" s="3">
-        <v>2710200</v>
+        <v>2779200</v>
       </c>
       <c r="K59" s="3">
         <v>1878300</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>20055300</v>
+        <v>20566100</v>
       </c>
       <c r="E60" s="3">
-        <v>22844900</v>
+        <v>23426700</v>
       </c>
       <c r="F60" s="3">
-        <v>19378400</v>
+        <v>19872000</v>
       </c>
       <c r="G60" s="3">
-        <v>19805800</v>
+        <v>20310200</v>
       </c>
       <c r="H60" s="3">
-        <v>24086100</v>
+        <v>24699500</v>
       </c>
       <c r="I60" s="3">
-        <v>20894800</v>
+        <v>21426900</v>
       </c>
       <c r="J60" s="3">
-        <v>19968300</v>
+        <v>20476900</v>
       </c>
       <c r="K60" s="3">
         <v>14708600</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>45305900</v>
+        <v>46459800</v>
       </c>
       <c r="E61" s="3">
-        <v>49554200</v>
+        <v>50816300</v>
       </c>
       <c r="F61" s="3">
-        <v>45638600</v>
+        <v>46800900</v>
       </c>
       <c r="G61" s="3">
-        <v>51091000</v>
+        <v>52392200</v>
       </c>
       <c r="H61" s="3">
-        <v>48374400</v>
+        <v>49606400</v>
       </c>
       <c r="I61" s="3">
-        <v>55386600</v>
+        <v>56797300</v>
       </c>
       <c r="J61" s="3">
-        <v>56337400</v>
+        <v>57772200</v>
       </c>
       <c r="K61" s="3">
         <v>20455000</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>18814100</v>
+        <v>19293300</v>
       </c>
       <c r="E62" s="3">
-        <v>27200700</v>
+        <v>27893400</v>
       </c>
       <c r="F62" s="3">
-        <v>24509600</v>
+        <v>25133900</v>
       </c>
       <c r="G62" s="3">
-        <v>24734900</v>
+        <v>25364800</v>
       </c>
       <c r="H62" s="3">
-        <v>25871200</v>
+        <v>26530100</v>
       </c>
       <c r="I62" s="3">
-        <v>26924300</v>
+        <v>27610000</v>
       </c>
       <c r="J62" s="3">
-        <v>26609500</v>
+        <v>27287200</v>
       </c>
       <c r="K62" s="3">
         <v>3750300</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>84646200</v>
+        <v>86802000</v>
       </c>
       <c r="E66" s="3">
-        <v>100037000</v>
+        <v>102585000</v>
       </c>
       <c r="F66" s="3">
-        <v>89910500</v>
+        <v>92200400</v>
       </c>
       <c r="G66" s="3">
-        <v>95992500</v>
+        <v>98437300</v>
       </c>
       <c r="H66" s="3">
-        <v>98661800</v>
+        <v>101175000</v>
       </c>
       <c r="I66" s="3">
-        <v>103518000</v>
+        <v>106154000</v>
       </c>
       <c r="J66" s="3">
-        <v>102746000</v>
+        <v>105363000</v>
       </c>
       <c r="K66" s="3">
         <v>39191800</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>75132300</v>
+        <v>77045800</v>
       </c>
       <c r="E72" s="3">
-        <v>100174000</v>
+        <v>102726000</v>
       </c>
       <c r="F72" s="3">
-        <v>97790400</v>
+        <v>100281000</v>
       </c>
       <c r="G72" s="3">
-        <v>95048200</v>
+        <v>97468900</v>
       </c>
       <c r="H72" s="3">
-        <v>92877900</v>
+        <v>95243400</v>
       </c>
       <c r="I72" s="3">
-        <v>90707700</v>
+        <v>93017900</v>
       </c>
       <c r="J72" s="3">
-        <v>131494000</v>
+        <v>134843000</v>
       </c>
       <c r="K72" s="3">
         <v>9419900</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>67264000</v>
+        <v>68977100</v>
       </c>
       <c r="E76" s="3">
-        <v>96441600</v>
+        <v>98897900</v>
       </c>
       <c r="F76" s="3">
-        <v>85863100</v>
+        <v>88049900</v>
       </c>
       <c r="G76" s="3">
-        <v>80197000</v>
+        <v>82239500</v>
       </c>
       <c r="H76" s="3">
-        <v>81769600</v>
+        <v>83852200</v>
       </c>
       <c r="I76" s="3">
-        <v>83742800</v>
+        <v>85875600</v>
       </c>
       <c r="J76" s="3">
-        <v>77747800</v>
+        <v>79728000</v>
       </c>
       <c r="K76" s="3">
         <v>10150600</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-18384200</v>
+        <v>-18852400</v>
       </c>
       <c r="E81" s="3">
-        <v>8529900</v>
+        <v>8747100</v>
       </c>
       <c r="F81" s="3">
-        <v>8702600</v>
+        <v>8924300</v>
       </c>
       <c r="G81" s="3">
-        <v>8189500</v>
+        <v>8398100</v>
       </c>
       <c r="H81" s="3">
-        <v>7298900</v>
+        <v>7484800</v>
       </c>
       <c r="I81" s="3">
-        <v>7718600</v>
+        <v>7915200</v>
       </c>
       <c r="J81" s="3">
-        <v>47966200</v>
+        <v>49187800</v>
       </c>
       <c r="K81" s="3">
         <v>5766300</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>36614800</v>
+        <v>37547300</v>
       </c>
       <c r="E83" s="3">
-        <v>1669900</v>
+        <v>1712400</v>
       </c>
       <c r="F83" s="3">
-        <v>1376900</v>
+        <v>1411900</v>
       </c>
       <c r="G83" s="3">
-        <v>1662200</v>
+        <v>1704500</v>
       </c>
       <c r="H83" s="3">
-        <v>1854200</v>
+        <v>1901400</v>
       </c>
       <c r="I83" s="3">
-        <v>1266800</v>
+        <v>1299100</v>
       </c>
       <c r="J83" s="3">
-        <v>1045400</v>
+        <v>1072100</v>
       </c>
       <c r="K83" s="3">
         <v>753000</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>14180600</v>
+        <v>14541800</v>
       </c>
       <c r="E89" s="3">
-        <v>12829400</v>
+        <v>13156100</v>
       </c>
       <c r="F89" s="3">
-        <v>12434000</v>
+        <v>12750600</v>
       </c>
       <c r="G89" s="3">
-        <v>12522300</v>
+        <v>12841200</v>
       </c>
       <c r="H89" s="3">
-        <v>11511400</v>
+        <v>11804600</v>
       </c>
       <c r="I89" s="3">
-        <v>13173600</v>
+        <v>13509100</v>
       </c>
       <c r="J89" s="3">
-        <v>6842100</v>
+        <v>7016300</v>
       </c>
       <c r="K89" s="3">
         <v>5719200</v>
@@ -4029,25 +4029,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-588600</v>
+        <v>-603600</v>
       </c>
       <c r="E91" s="3">
-        <v>-669200</v>
+        <v>-686300</v>
       </c>
       <c r="F91" s="3">
-        <v>-674400</v>
+        <v>-691500</v>
       </c>
       <c r="G91" s="3">
-        <v>-653900</v>
+        <v>-670500</v>
       </c>
       <c r="H91" s="3">
-        <v>-849700</v>
+        <v>-871300</v>
       </c>
       <c r="I91" s="3">
-        <v>-969900</v>
+        <v>-994600</v>
       </c>
       <c r="J91" s="3">
-        <v>-1012200</v>
+        <v>-1038000</v>
       </c>
       <c r="K91" s="3">
         <v>-727000</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-378800</v>
+        <v>-388400</v>
       </c>
       <c r="E94" s="3">
-        <v>-902100</v>
+        <v>-925100</v>
       </c>
       <c r="F94" s="3">
-        <v>-1458800</v>
+        <v>-1495900</v>
       </c>
       <c r="G94" s="3">
-        <v>-1001900</v>
+        <v>-1027500</v>
       </c>
       <c r="H94" s="3">
-        <v>-817700</v>
+        <v>-838500</v>
       </c>
       <c r="I94" s="3">
-        <v>-1306500</v>
+        <v>-1339800</v>
       </c>
       <c r="J94" s="3">
-        <v>-23729100</v>
+        <v>-24333400</v>
       </c>
       <c r="K94" s="3">
         <v>-794000</v>
@@ -4228,25 +4228,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-6468400</v>
+        <v>-6633200</v>
       </c>
       <c r="E96" s="3">
-        <v>-6289300</v>
+        <v>-6449500</v>
       </c>
       <c r="F96" s="3">
-        <v>-6275200</v>
+        <v>-6435000</v>
       </c>
       <c r="G96" s="3">
-        <v>-6071700</v>
+        <v>-6226400</v>
       </c>
       <c r="H96" s="3">
-        <v>-5883600</v>
+        <v>-6033500</v>
       </c>
       <c r="I96" s="3">
-        <v>-5562500</v>
+        <v>-5704100</v>
       </c>
       <c r="J96" s="3">
-        <v>-4433800</v>
+        <v>-4546800</v>
       </c>
       <c r="K96" s="3">
         <v>-3610100</v>
@@ -4408,25 +4408,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-11918300</v>
+        <v>-12221800</v>
       </c>
       <c r="E100" s="3">
-        <v>-11360400</v>
+        <v>-11649700</v>
       </c>
       <c r="F100" s="3">
-        <v>-11195300</v>
+        <v>-11480400</v>
       </c>
       <c r="G100" s="3">
-        <v>-10105100</v>
+        <v>-10362400</v>
       </c>
       <c r="H100" s="3">
-        <v>-10995700</v>
+        <v>-11275700</v>
       </c>
       <c r="I100" s="3">
-        <v>-12322600</v>
+        <v>-12636500</v>
       </c>
       <c r="J100" s="3">
-        <v>18885800</v>
+        <v>19366800</v>
       </c>
       <c r="K100" s="3">
         <v>-5246500</v>
@@ -4453,25 +4453,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-373600</v>
+        <v>-383200</v>
       </c>
       <c r="E101" s="3">
-        <v>551500</v>
+        <v>565600</v>
       </c>
       <c r="F101" s="3">
-        <v>-323700</v>
+        <v>-332000</v>
       </c>
       <c r="G101" s="3">
-        <v>-323700</v>
+        <v>-332000</v>
       </c>
       <c r="H101" s="3">
-        <v>-72900</v>
+        <v>-74800</v>
       </c>
       <c r="I101" s="3">
-        <v>-176600</v>
+        <v>-181100</v>
       </c>
       <c r="J101" s="3">
-        <v>-500300</v>
+        <v>-513100</v>
       </c>
       <c r="K101" s="3">
         <v>223300</v>
@@ -4498,25 +4498,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1509900</v>
+        <v>1548400</v>
       </c>
       <c r="E102" s="3">
-        <v>1118400</v>
+        <v>1146900</v>
       </c>
       <c r="F102" s="3">
-        <v>-543800</v>
+        <v>-557700</v>
       </c>
       <c r="G102" s="3">
-        <v>1091500</v>
+        <v>1119300</v>
       </c>
       <c r="H102" s="3">
-        <v>-374900</v>
+        <v>-384500</v>
       </c>
       <c r="I102" s="3">
-        <v>-632100</v>
+        <v>-648200</v>
       </c>
       <c r="J102" s="3">
-        <v>1498400</v>
+        <v>1536600</v>
       </c>
       <c r="K102" s="3">
         <v>-98000</v>

--- a/AAII_Financials/Yearly/BTI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BTI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
   <si>
     <t>BTI</t>
   </si>
@@ -727,25 +727,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>35800800</v>
+        <v>34751900</v>
       </c>
       <c r="E8" s="3">
-        <v>36288900</v>
+        <v>33321300</v>
       </c>
       <c r="F8" s="3">
-        <v>33702500</v>
+        <v>34777700</v>
       </c>
       <c r="G8" s="3">
-        <v>33823300</v>
+        <v>35192000</v>
       </c>
       <c r="H8" s="3">
-        <v>33955800</v>
+        <v>34271900</v>
       </c>
       <c r="I8" s="3">
-        <v>32138400</v>
+        <v>31215500</v>
       </c>
       <c r="J8" s="3">
-        <v>25671900</v>
+        <v>26443200</v>
       </c>
       <c r="K8" s="3">
         <v>17529700</v>
@@ -772,25 +772,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6418000</v>
+        <v>6229900</v>
       </c>
       <c r="E9" s="3">
-        <v>6303800</v>
+        <v>5788300</v>
       </c>
       <c r="F9" s="3">
-        <v>6032200</v>
+        <v>6224600</v>
       </c>
       <c r="G9" s="3">
-        <v>5429900</v>
+        <v>6071500</v>
       </c>
       <c r="H9" s="3">
-        <v>5822200</v>
+        <v>5908200</v>
       </c>
       <c r="I9" s="3">
-        <v>5970500</v>
+        <v>5859000</v>
       </c>
       <c r="J9" s="3">
-        <v>6604300</v>
+        <v>6802700</v>
       </c>
       <c r="K9" s="3">
         <v>4631200</v>
@@ -817,25 +817,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>29382800</v>
+        <v>28521900</v>
       </c>
       <c r="E10" s="3">
-        <v>29985100</v>
+        <v>27533000</v>
       </c>
       <c r="F10" s="3">
-        <v>27670400</v>
+        <v>28553100</v>
       </c>
       <c r="G10" s="3">
-        <v>28393400</v>
+        <v>29120500</v>
       </c>
       <c r="H10" s="3">
-        <v>28133600</v>
+        <v>28363700</v>
       </c>
       <c r="I10" s="3">
-        <v>26167900</v>
+        <v>25356500</v>
       </c>
       <c r="J10" s="3">
-        <v>19067600</v>
+        <v>19640500</v>
       </c>
       <c r="K10" s="3">
         <v>12898500</v>
@@ -881,25 +881,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>237500</v>
+        <v>519700</v>
       </c>
       <c r="E12" s="3">
-        <v>181100</v>
+        <v>389200</v>
       </c>
       <c r="F12" s="3">
-        <v>185000</v>
+        <v>411600</v>
       </c>
       <c r="G12" s="3">
-        <v>158800</v>
+        <v>419100</v>
       </c>
       <c r="H12" s="3">
-        <v>165300</v>
-      </c>
-      <c r="I12" s="3">
-        <v>137800</v>
+        <v>498000</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J12" s="3">
-        <v>105000</v>
+        <v>258200</v>
       </c>
       <c r="K12" s="3">
         <v>65800</v>
@@ -971,25 +971,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>37050000</v>
+        <v>36207800</v>
       </c>
       <c r="E14" s="3">
-        <v>1068100</v>
+        <v>1286800</v>
       </c>
       <c r="F14" s="3">
-        <v>851600</v>
+        <v>942400</v>
       </c>
       <c r="G14" s="3">
-        <v>999900</v>
+        <v>1369400</v>
       </c>
       <c r="H14" s="3">
-        <v>999900</v>
+        <v>1920400</v>
       </c>
       <c r="I14" s="3">
-        <v>421200</v>
+        <v>906200</v>
       </c>
       <c r="J14" s="3">
-        <v>-29570400</v>
+        <v>1284000</v>
       </c>
       <c r="K14" s="3">
         <v>873400</v>
@@ -1016,25 +1016,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1132400</v>
+        <v>1081400</v>
       </c>
       <c r="E15" s="3">
-        <v>1280700</v>
+        <v>1159100</v>
       </c>
       <c r="F15" s="3">
-        <v>1245300</v>
+        <v>1394700</v>
       </c>
       <c r="G15" s="3">
-        <v>1430300</v>
+        <v>1488200</v>
       </c>
       <c r="H15" s="3">
-        <v>1646800</v>
+        <v>1316500</v>
       </c>
       <c r="I15" s="3">
-        <v>1299100</v>
+        <v>1019600</v>
       </c>
       <c r="J15" s="3">
-        <v>1072100</v>
+        <v>977200</v>
       </c>
       <c r="K15" s="3">
         <v>1346100</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>56303900</v>
+        <v>18650300</v>
       </c>
       <c r="E17" s="3">
-        <v>22480600</v>
+        <v>19281900</v>
       </c>
       <c r="F17" s="3">
-        <v>20273500</v>
+        <v>20007600</v>
       </c>
       <c r="G17" s="3">
-        <v>20937500</v>
+        <v>20251500</v>
       </c>
       <c r="H17" s="3">
-        <v>22125000</v>
+        <v>20480800</v>
       </c>
       <c r="I17" s="3">
-        <v>19858800</v>
+        <v>18429500</v>
       </c>
       <c r="J17" s="3">
-        <v>-13099700</v>
+        <v>16753400</v>
       </c>
       <c r="K17" s="3">
         <v>11880000</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-20503100</v>
+        <v>16101500</v>
       </c>
       <c r="E18" s="3">
-        <v>13808300</v>
+        <v>14039400</v>
       </c>
       <c r="F18" s="3">
-        <v>13429100</v>
+        <v>14770100</v>
       </c>
       <c r="G18" s="3">
-        <v>12885800</v>
+        <v>14940500</v>
       </c>
       <c r="H18" s="3">
-        <v>11830800</v>
+        <v>13791100</v>
       </c>
       <c r="I18" s="3">
-        <v>12279600</v>
+        <v>12786000</v>
       </c>
       <c r="J18" s="3">
-        <v>38771600</v>
+        <v>9689800</v>
       </c>
       <c r="K18" s="3">
         <v>5649700</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>523600</v>
+        <v>-501900</v>
       </c>
       <c r="E20" s="3">
-        <v>561600</v>
+        <v>-331300</v>
       </c>
       <c r="F20" s="3">
-        <v>510400</v>
+        <v>-524000</v>
       </c>
       <c r="G20" s="3">
-        <v>633800</v>
+        <v>-641700</v>
       </c>
       <c r="H20" s="3">
-        <v>792600</v>
+        <v>-864800</v>
       </c>
       <c r="I20" s="3">
-        <v>768900</v>
+        <v>-759600</v>
       </c>
       <c r="J20" s="3">
-        <v>1392200</v>
+        <v>-32875600</v>
       </c>
       <c r="K20" s="3">
         <v>2898000</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>17570600</v>
+        <v>17684800</v>
       </c>
       <c r="E21" s="3">
-        <v>16082500</v>
+        <v>15529900</v>
       </c>
       <c r="F21" s="3">
-        <v>15351500</v>
+        <v>16688800</v>
       </c>
       <c r="G21" s="3">
-        <v>15224300</v>
+        <v>17070300</v>
       </c>
       <c r="H21" s="3">
-        <v>14524900</v>
+        <v>15972500</v>
       </c>
       <c r="I21" s="3">
-        <v>14347700</v>
+        <v>14565200</v>
       </c>
       <c r="J21" s="3">
-        <v>41236000</v>
+        <v>43542600</v>
       </c>
       <c r="K21" s="3">
         <v>9301500</v>
@@ -1276,25 +1276,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2407900</v>
+        <v>2364100</v>
       </c>
       <c r="E22" s="3">
-        <v>2134900</v>
+        <v>1960400</v>
       </c>
       <c r="F22" s="3">
-        <v>1915800</v>
+        <v>1991800</v>
       </c>
       <c r="G22" s="3">
-        <v>2140200</v>
+        <v>2441200</v>
       </c>
       <c r="H22" s="3">
-        <v>2241200</v>
+        <v>2368100</v>
       </c>
       <c r="I22" s="3">
-        <v>2090300</v>
+        <v>2082600</v>
       </c>
       <c r="J22" s="3">
-        <v>1418500</v>
+        <v>1485400</v>
       </c>
       <c r="K22" s="3">
         <v>800200</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-22387400</v>
+        <v>-21731500</v>
       </c>
       <c r="E23" s="3">
-        <v>12235000</v>
+        <v>11234400</v>
       </c>
       <c r="F23" s="3">
-        <v>12023700</v>
+        <v>12407200</v>
       </c>
       <c r="G23" s="3">
-        <v>11379400</v>
+        <v>11839900</v>
       </c>
       <c r="H23" s="3">
-        <v>10382100</v>
+        <v>10478800</v>
       </c>
       <c r="I23" s="3">
-        <v>10958200</v>
+        <v>10643500</v>
       </c>
       <c r="J23" s="3">
-        <v>38745300</v>
+        <v>39909400</v>
       </c>
       <c r="K23" s="3">
         <v>7747500</v>
@@ -1366,25 +1366,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-3768600</v>
+        <v>-3658200</v>
       </c>
       <c r="E24" s="3">
-        <v>3251600</v>
+        <v>2985700</v>
       </c>
       <c r="F24" s="3">
-        <v>3079700</v>
+        <v>2964000</v>
       </c>
       <c r="G24" s="3">
-        <v>2940600</v>
+        <v>2878100</v>
       </c>
       <c r="H24" s="3">
-        <v>2768700</v>
+        <v>2732300</v>
       </c>
       <c r="I24" s="3">
-        <v>2901300</v>
+        <v>2728700</v>
       </c>
       <c r="J24" s="3">
-        <v>1911900</v>
+        <v>-10987400</v>
       </c>
       <c r="K24" s="3">
         <v>1744300</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-18618800</v>
+        <v>-18073300</v>
       </c>
       <c r="E26" s="3">
-        <v>8983300</v>
+        <v>8248700</v>
       </c>
       <c r="F26" s="3">
-        <v>8944000</v>
+        <v>9443200</v>
       </c>
       <c r="G26" s="3">
-        <v>8438800</v>
+        <v>8961800</v>
       </c>
       <c r="H26" s="3">
-        <v>7613400</v>
+        <v>7746500</v>
       </c>
       <c r="I26" s="3">
-        <v>8056900</v>
+        <v>7914800</v>
       </c>
       <c r="J26" s="3">
-        <v>36833500</v>
+        <v>50896800</v>
       </c>
       <c r="K26" s="3">
         <v>6003300</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-18852400</v>
+        <v>-18357400</v>
       </c>
       <c r="E27" s="3">
-        <v>8747100</v>
+        <v>7972800</v>
       </c>
       <c r="F27" s="3">
-        <v>8716900</v>
+        <v>9192700</v>
       </c>
       <c r="G27" s="3">
-        <v>8223600</v>
+        <v>8737900</v>
       </c>
       <c r="H27" s="3">
-        <v>7423100</v>
+        <v>7554500</v>
       </c>
       <c r="I27" s="3">
-        <v>7823300</v>
+        <v>7687900</v>
       </c>
       <c r="J27" s="3">
-        <v>36609100</v>
+        <v>50665700</v>
       </c>
       <c r="K27" s="3">
         <v>5766300</v>
@@ -1590,26 +1590,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>207300</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>174500</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>61700</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>91900</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>12578700</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-523600</v>
+        <v>501900</v>
       </c>
       <c r="E32" s="3">
-        <v>-561600</v>
+        <v>331300</v>
       </c>
       <c r="F32" s="3">
-        <v>-510400</v>
+        <v>524000</v>
       </c>
       <c r="G32" s="3">
-        <v>-633800</v>
+        <v>641700</v>
       </c>
       <c r="H32" s="3">
-        <v>-792600</v>
+        <v>864800</v>
       </c>
       <c r="I32" s="3">
-        <v>-768900</v>
+        <v>759600</v>
       </c>
       <c r="J32" s="3">
-        <v>-1392200</v>
+        <v>32875600</v>
       </c>
       <c r="K32" s="3">
         <v>-2898000</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-18852400</v>
+        <v>-18300000</v>
       </c>
       <c r="E33" s="3">
-        <v>8747100</v>
+        <v>8031800</v>
       </c>
       <c r="F33" s="3">
-        <v>8924300</v>
+        <v>9209000</v>
       </c>
       <c r="G33" s="3">
-        <v>8398100</v>
+        <v>8737900</v>
       </c>
       <c r="H33" s="3">
-        <v>7484800</v>
+        <v>7554500</v>
       </c>
       <c r="I33" s="3">
-        <v>7915200</v>
+        <v>7687900</v>
       </c>
       <c r="J33" s="3">
-        <v>49187800</v>
+        <v>50665700</v>
       </c>
       <c r="K33" s="3">
         <v>5766300</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-18852400</v>
+        <v>-18300000</v>
       </c>
       <c r="E35" s="3">
-        <v>8747100</v>
+        <v>8031800</v>
       </c>
       <c r="F35" s="3">
-        <v>8924300</v>
+        <v>9209000</v>
       </c>
       <c r="G35" s="3">
-        <v>8398100</v>
+        <v>8737900</v>
       </c>
       <c r="H35" s="3">
-        <v>7484800</v>
+        <v>7554500</v>
       </c>
       <c r="I35" s="3">
-        <v>7915200</v>
+        <v>7687900</v>
       </c>
       <c r="J35" s="3">
-        <v>49187800</v>
+        <v>50665700</v>
       </c>
       <c r="K35" s="3">
         <v>5766300</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6113500</v>
+        <v>5934400</v>
       </c>
       <c r="E41" s="3">
-        <v>4521800</v>
+        <v>4152100</v>
       </c>
       <c r="F41" s="3">
-        <v>3686000</v>
+        <v>3803600</v>
       </c>
       <c r="G41" s="3">
-        <v>4119000</v>
+        <v>4285700</v>
       </c>
       <c r="H41" s="3">
-        <v>3314600</v>
+        <v>3345500</v>
       </c>
       <c r="I41" s="3">
-        <v>3414300</v>
+        <v>3316300</v>
       </c>
       <c r="J41" s="3">
-        <v>8636900</v>
+        <v>4448200</v>
       </c>
       <c r="K41" s="3">
         <v>2734300</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>788600</v>
+        <v>765500</v>
       </c>
       <c r="E42" s="3">
-        <v>759800</v>
+        <v>697600</v>
       </c>
       <c r="F42" s="3">
-        <v>598400</v>
+        <v>617500</v>
       </c>
       <c r="G42" s="3">
-        <v>317600</v>
+        <v>330400</v>
       </c>
       <c r="H42" s="3">
-        <v>161400</v>
+        <v>162900</v>
       </c>
       <c r="I42" s="3">
-        <v>233600</v>
+        <v>226900</v>
       </c>
       <c r="J42" s="3">
-        <v>85300</v>
+        <v>87900</v>
       </c>
       <c r="K42" s="3">
         <v>18600</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4977200</v>
+        <v>4831400</v>
       </c>
       <c r="E43" s="3">
-        <v>5925900</v>
+        <v>5441300</v>
       </c>
       <c r="F43" s="3">
-        <v>5338000</v>
+        <v>5508300</v>
       </c>
       <c r="G43" s="3">
-        <v>4986400</v>
+        <v>5188100</v>
       </c>
       <c r="H43" s="3">
-        <v>5530900</v>
+        <v>5582400</v>
       </c>
       <c r="I43" s="3">
-        <v>4805300</v>
+        <v>4667300</v>
       </c>
       <c r="J43" s="3">
-        <v>5922000</v>
+        <v>6099900</v>
       </c>
       <c r="K43" s="3">
         <v>4904100</v>
@@ -2129,25 +2129,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6479600</v>
+        <v>6289800</v>
       </c>
       <c r="E44" s="3">
-        <v>7441500</v>
+        <v>6832900</v>
       </c>
       <c r="F44" s="3">
-        <v>6927100</v>
+        <v>7148100</v>
       </c>
       <c r="G44" s="3">
-        <v>7870600</v>
+        <v>8189100</v>
       </c>
       <c r="H44" s="3">
-        <v>7996500</v>
+        <v>8071000</v>
       </c>
       <c r="I44" s="3">
-        <v>7911300</v>
+        <v>7684100</v>
       </c>
       <c r="J44" s="3">
-        <v>15389500</v>
+        <v>7925900</v>
       </c>
       <c r="K44" s="3">
         <v>7186800</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>255900</v>
+        <v>248400</v>
       </c>
       <c r="E45" s="3">
-        <v>1570700</v>
+        <v>1442300</v>
       </c>
       <c r="F45" s="3">
-        <v>255900</v>
+        <v>264000</v>
       </c>
       <c r="G45" s="3">
-        <v>568200</v>
+        <v>591200</v>
       </c>
       <c r="H45" s="3">
-        <v>414700</v>
+        <v>418500</v>
       </c>
       <c r="I45" s="3">
-        <v>241400</v>
+        <v>234500</v>
       </c>
       <c r="J45" s="3">
-        <v>305700</v>
+        <v>314900</v>
       </c>
       <c r="K45" s="3">
         <v>488800</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>18614900</v>
+        <v>18069500</v>
       </c>
       <c r="E46" s="3">
-        <v>20219700</v>
+        <v>18566200</v>
       </c>
       <c r="F46" s="3">
-        <v>16805300</v>
+        <v>17341400</v>
       </c>
       <c r="G46" s="3">
-        <v>17861700</v>
+        <v>18584500</v>
       </c>
       <c r="H46" s="3">
-        <v>17418100</v>
+        <v>17580300</v>
       </c>
       <c r="I46" s="3">
-        <v>16605900</v>
+        <v>16129000</v>
       </c>
       <c r="J46" s="3">
-        <v>18326200</v>
+        <v>18876800</v>
       </c>
       <c r="K46" s="3">
         <v>15332600</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3161100</v>
+        <v>2659600</v>
       </c>
       <c r="E47" s="3">
-        <v>3125700</v>
+        <v>2579700</v>
       </c>
       <c r="F47" s="3">
-        <v>2897300</v>
+        <v>2705400</v>
       </c>
       <c r="G47" s="3">
-        <v>2703100</v>
+        <v>2482100</v>
       </c>
       <c r="H47" s="3">
-        <v>2781900</v>
+        <v>2479300</v>
       </c>
       <c r="I47" s="3">
-        <v>3229300</v>
+        <v>2263500</v>
       </c>
       <c r="J47" s="3">
-        <v>3116500</v>
+        <v>2188300</v>
       </c>
       <c r="K47" s="3">
         <v>12590800</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6013800</v>
+        <v>5837600</v>
       </c>
       <c r="E48" s="3">
-        <v>6386500</v>
+        <v>5864200</v>
       </c>
       <c r="F48" s="3">
-        <v>6499300</v>
+        <v>6706700</v>
       </c>
       <c r="G48" s="3">
-        <v>6639700</v>
+        <v>6908400</v>
       </c>
       <c r="H48" s="3">
-        <v>7240700</v>
+        <v>7308100</v>
       </c>
       <c r="I48" s="3">
-        <v>6778800</v>
+        <v>6584200</v>
       </c>
       <c r="J48" s="3">
-        <v>12812300</v>
+        <v>6598600</v>
       </c>
       <c r="K48" s="3">
         <v>4541800</v>
@@ -2354,25 +2354,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>125397000</v>
+        <v>121722600</v>
       </c>
       <c r="E49" s="3">
-        <v>169372000</v>
+        <v>155521400</v>
       </c>
       <c r="F49" s="3">
-        <v>151723000</v>
+        <v>156563100</v>
       </c>
       <c r="G49" s="3">
-        <v>151353000</v>
+        <v>157477700</v>
       </c>
       <c r="H49" s="3">
-        <v>155872000</v>
+        <v>157323400</v>
       </c>
       <c r="I49" s="3">
-        <v>162730000</v>
+        <v>158056900</v>
       </c>
       <c r="J49" s="3">
-        <v>309115000</v>
+        <v>159201200</v>
       </c>
       <c r="K49" s="3">
         <v>15032400</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2592900</v>
+        <v>1765400</v>
       </c>
       <c r="E52" s="3">
-        <v>2379000</v>
+        <v>1653100</v>
       </c>
       <c r="F52" s="3">
-        <v>2325200</v>
+        <v>1856400</v>
       </c>
       <c r="G52" s="3">
-        <v>2119200</v>
+        <v>1806300</v>
       </c>
       <c r="H52" s="3">
-        <v>1713700</v>
+        <v>1496600</v>
       </c>
       <c r="I52" s="3">
-        <v>2686100</v>
+        <v>3043600</v>
       </c>
       <c r="J52" s="3">
-        <v>2684800</v>
+        <v>3337200</v>
       </c>
       <c r="K52" s="3">
         <v>1844800</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>155779000</v>
+        <v>151215200</v>
       </c>
       <c r="E54" s="3">
-        <v>201483000</v>
+        <v>185006300</v>
       </c>
       <c r="F54" s="3">
-        <v>180250000</v>
+        <v>186000400</v>
       </c>
       <c r="G54" s="3">
-        <v>180677000</v>
+        <v>187988100</v>
       </c>
       <c r="H54" s="3">
-        <v>185027000</v>
+        <v>186749200</v>
       </c>
       <c r="I54" s="3">
-        <v>192030000</v>
+        <v>186515600</v>
       </c>
       <c r="J54" s="3">
-        <v>185091000</v>
+        <v>190652200</v>
       </c>
       <c r="K54" s="3">
         <v>49342400</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>12728300</v>
+        <v>2174300</v>
       </c>
       <c r="E57" s="3">
-        <v>13711200</v>
+        <v>2243500</v>
       </c>
       <c r="F57" s="3">
-        <v>12566900</v>
+        <v>5312000</v>
       </c>
       <c r="G57" s="3">
-        <v>12719200</v>
+        <v>5081600</v>
       </c>
       <c r="H57" s="3">
-        <v>12763800</v>
+        <v>4573200</v>
       </c>
       <c r="I57" s="3">
-        <v>13950000</v>
+        <v>4533500</v>
       </c>
       <c r="J57" s="3">
-        <v>11689100</v>
+        <v>3106000</v>
       </c>
       <c r="K57" s="3">
         <v>9099800</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4922100</v>
+        <v>5507700</v>
       </c>
       <c r="E58" s="3">
-        <v>5103100</v>
+        <v>5334100</v>
       </c>
       <c r="F58" s="3">
-        <v>4634700</v>
+        <v>5405400</v>
       </c>
       <c r="G58" s="3">
-        <v>4647800</v>
+        <v>5517200</v>
       </c>
       <c r="H58" s="3">
-        <v>9300900</v>
+        <v>10015200</v>
       </c>
       <c r="I58" s="3">
-        <v>4927300</v>
+        <v>5384800</v>
       </c>
       <c r="J58" s="3">
-        <v>13648200</v>
+        <v>7329900</v>
       </c>
       <c r="K58" s="3">
         <v>3730500</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2915700</v>
+        <v>12265000</v>
       </c>
       <c r="E59" s="3">
-        <v>4612400</v>
+        <v>13916500</v>
       </c>
       <c r="F59" s="3">
-        <v>2670300</v>
+        <v>9769500</v>
       </c>
       <c r="G59" s="3">
-        <v>2943300</v>
+        <v>10501900</v>
       </c>
       <c r="H59" s="3">
-        <v>2634900</v>
+        <v>10322500</v>
       </c>
       <c r="I59" s="3">
-        <v>2549600</v>
+        <v>10871600</v>
       </c>
       <c r="J59" s="3">
-        <v>2779200</v>
+        <v>10623800</v>
       </c>
       <c r="K59" s="3">
         <v>1878300</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>20566100</v>
+        <v>19963600</v>
       </c>
       <c r="E60" s="3">
-        <v>23426700</v>
+        <v>21510900</v>
       </c>
       <c r="F60" s="3">
-        <v>19872000</v>
+        <v>20505900</v>
       </c>
       <c r="G60" s="3">
-        <v>20310200</v>
+        <v>21132100</v>
       </c>
       <c r="H60" s="3">
-        <v>24699500</v>
+        <v>24929500</v>
       </c>
       <c r="I60" s="3">
-        <v>21426900</v>
+        <v>20811600</v>
       </c>
       <c r="J60" s="3">
-        <v>20476900</v>
+        <v>21092100</v>
       </c>
       <c r="K60" s="3">
         <v>14708600</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>46459800</v>
+        <v>45336800</v>
       </c>
       <c r="E61" s="3">
-        <v>50816300</v>
+        <v>47184800</v>
       </c>
       <c r="F61" s="3">
-        <v>46800900</v>
+        <v>48293900</v>
       </c>
       <c r="G61" s="3">
-        <v>52392200</v>
+        <v>54512300</v>
       </c>
       <c r="H61" s="3">
-        <v>49606400</v>
+        <v>50068200</v>
       </c>
       <c r="I61" s="3">
-        <v>56797300</v>
+        <v>55166300</v>
       </c>
       <c r="J61" s="3">
-        <v>57772200</v>
+        <v>59508000</v>
       </c>
       <c r="K61" s="3">
         <v>20455000</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>19293300</v>
+        <v>1801100</v>
       </c>
       <c r="E62" s="3">
-        <v>27893400</v>
+        <v>1704900</v>
       </c>
       <c r="F62" s="3">
-        <v>25133900</v>
+        <v>1930900</v>
       </c>
       <c r="G62" s="3">
-        <v>25364800</v>
+        <v>2016500</v>
       </c>
       <c r="H62" s="3">
-        <v>26530100</v>
+        <v>2244900</v>
       </c>
       <c r="I62" s="3">
-        <v>27610000</v>
+        <v>2018800</v>
       </c>
       <c r="J62" s="3">
-        <v>27287200</v>
+        <v>2015300</v>
       </c>
       <c r="K62" s="3">
         <v>3750300</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>86802000</v>
+        <v>83790200</v>
       </c>
       <c r="E66" s="3">
-        <v>102585000</v>
+        <v>93784000</v>
       </c>
       <c r="F66" s="3">
-        <v>92200400</v>
+        <v>94735400</v>
       </c>
       <c r="G66" s="3">
-        <v>98437300</v>
+        <v>102035700</v>
       </c>
       <c r="H66" s="3">
-        <v>101175000</v>
+        <v>101774700</v>
       </c>
       <c r="I66" s="3">
-        <v>106154000</v>
+        <v>102795000</v>
       </c>
       <c r="J66" s="3">
-        <v>105363000</v>
+        <v>108228700</v>
       </c>
       <c r="K66" s="3">
         <v>39191800</v>
@@ -3230,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>122900</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>119200</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>114700</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>121600</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>77045800</v>
+        <v>40285100</v>
       </c>
       <c r="E72" s="3">
-        <v>102726000</v>
+        <v>61686800</v>
       </c>
       <c r="F72" s="3">
-        <v>100281000</v>
+        <v>66801200</v>
       </c>
       <c r="G72" s="3">
-        <v>97468900</v>
+        <v>64429900</v>
       </c>
       <c r="H72" s="3">
-        <v>95243400</v>
+        <v>60254300</v>
       </c>
       <c r="I72" s="3">
-        <v>93017900</v>
+        <v>55822600</v>
       </c>
       <c r="J72" s="3">
-        <v>134843000</v>
+        <v>56944000</v>
       </c>
       <c r="K72" s="3">
         <v>9419900</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>68977100</v>
+        <v>66956200</v>
       </c>
       <c r="E76" s="3">
-        <v>98897900</v>
+        <v>90810300</v>
       </c>
       <c r="F76" s="3">
-        <v>88049900</v>
+        <v>90858700</v>
       </c>
       <c r="G76" s="3">
-        <v>82239500</v>
+        <v>85444500</v>
       </c>
       <c r="H76" s="3">
-        <v>83852200</v>
+        <v>84513600</v>
       </c>
       <c r="I76" s="3">
-        <v>85875600</v>
+        <v>83294900</v>
       </c>
       <c r="J76" s="3">
-        <v>79728000</v>
+        <v>82001800</v>
       </c>
       <c r="K76" s="3">
         <v>10150600</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-18852400</v>
+        <v>-18300000</v>
       </c>
       <c r="E81" s="3">
-        <v>8747100</v>
+        <v>8031800</v>
       </c>
       <c r="F81" s="3">
-        <v>8924300</v>
+        <v>9209000</v>
       </c>
       <c r="G81" s="3">
-        <v>8398100</v>
+        <v>8737900</v>
       </c>
       <c r="H81" s="3">
-        <v>7484800</v>
+        <v>7554500</v>
       </c>
       <c r="I81" s="3">
-        <v>7915200</v>
+        <v>7687900</v>
       </c>
       <c r="J81" s="3">
-        <v>49187800</v>
+        <v>50665700</v>
       </c>
       <c r="K81" s="3">
         <v>5766300</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>37547300</v>
+        <v>626700</v>
       </c>
       <c r="E83" s="3">
-        <v>1712400</v>
+        <v>632600</v>
       </c>
       <c r="F83" s="3">
-        <v>1411900</v>
+        <v>769100</v>
       </c>
       <c r="G83" s="3">
-        <v>1704500</v>
+        <v>820500</v>
       </c>
       <c r="H83" s="3">
-        <v>1901400</v>
+        <v>1316500</v>
       </c>
       <c r="I83" s="3">
-        <v>1299100</v>
+        <v>1019600</v>
       </c>
       <c r="J83" s="3">
-        <v>1072100</v>
+        <v>977200</v>
       </c>
       <c r="K83" s="3">
         <v>753000</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>14541800</v>
+        <v>13647000</v>
       </c>
       <c r="E89" s="3">
-        <v>13156100</v>
+        <v>12523600</v>
       </c>
       <c r="F89" s="3">
-        <v>12750600</v>
+        <v>13157400</v>
       </c>
       <c r="G89" s="3">
-        <v>12841200</v>
+        <v>13360800</v>
       </c>
       <c r="H89" s="3">
-        <v>11804600</v>
+        <v>11914400</v>
       </c>
       <c r="I89" s="3">
-        <v>13509100</v>
+        <v>13121200</v>
       </c>
       <c r="J89" s="3">
-        <v>7016300</v>
+        <v>7227100</v>
       </c>
       <c r="K89" s="3">
         <v>5719200</v>
@@ -4029,25 +4029,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-603600</v>
+        <v>-585900</v>
       </c>
       <c r="E91" s="3">
-        <v>-686300</v>
+        <v>-630200</v>
       </c>
       <c r="F91" s="3">
-        <v>-691500</v>
+        <v>-713600</v>
       </c>
       <c r="G91" s="3">
-        <v>-670500</v>
+        <v>-697700</v>
       </c>
       <c r="H91" s="3">
-        <v>-871300</v>
+        <v>-879400</v>
       </c>
       <c r="I91" s="3">
-        <v>-994600</v>
+        <v>-966100</v>
       </c>
       <c r="J91" s="3">
-        <v>-1038000</v>
+        <v>-1069100</v>
       </c>
       <c r="K91" s="3">
         <v>-727000</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-388400</v>
+        <v>-377000</v>
       </c>
       <c r="E94" s="3">
-        <v>-925100</v>
+        <v>-849400</v>
       </c>
       <c r="F94" s="3">
-        <v>-1495900</v>
+        <v>-1543600</v>
       </c>
       <c r="G94" s="3">
-        <v>-1027500</v>
+        <v>-1069000</v>
       </c>
       <c r="H94" s="3">
-        <v>-838500</v>
+        <v>-846300</v>
       </c>
       <c r="I94" s="3">
-        <v>-1339800</v>
+        <v>-1301300</v>
       </c>
       <c r="J94" s="3">
-        <v>-24333400</v>
+        <v>-25064500</v>
       </c>
       <c r="K94" s="3">
         <v>-794000</v>
@@ -4228,25 +4228,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-6633200</v>
+        <v>6514000</v>
       </c>
       <c r="E96" s="3">
-        <v>-6449500</v>
+        <v>5994300</v>
       </c>
       <c r="F96" s="3">
-        <v>-6435000</v>
+        <v>6648400</v>
       </c>
       <c r="G96" s="3">
-        <v>-6226400</v>
+        <v>6478300</v>
       </c>
       <c r="H96" s="3">
-        <v>-6033500</v>
+        <v>6089700</v>
       </c>
       <c r="I96" s="3">
-        <v>-5704100</v>
+        <v>4260700</v>
       </c>
       <c r="J96" s="3">
-        <v>-4546800</v>
+        <v>4683400</v>
       </c>
       <c r="K96" s="3">
         <v>-3610100</v>
@@ -4408,25 +4408,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-12221800</v>
+        <v>-11863800</v>
       </c>
       <c r="E100" s="3">
-        <v>-11649700</v>
+        <v>-10697000</v>
       </c>
       <c r="F100" s="3">
-        <v>-11480400</v>
+        <v>-11846700</v>
       </c>
       <c r="G100" s="3">
-        <v>-10362400</v>
+        <v>-10781800</v>
       </c>
       <c r="H100" s="3">
-        <v>-11275700</v>
+        <v>-11380700</v>
       </c>
       <c r="I100" s="3">
-        <v>-12636500</v>
+        <v>-12273600</v>
       </c>
       <c r="J100" s="3">
-        <v>19366800</v>
+        <v>19948600</v>
       </c>
       <c r="K100" s="3">
         <v>-5246500</v>
@@ -4453,25 +4453,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-383200</v>
+        <v>-371900</v>
       </c>
       <c r="E101" s="3">
-        <v>565600</v>
+        <v>519300</v>
       </c>
       <c r="F101" s="3">
-        <v>-332000</v>
+        <v>-342600</v>
       </c>
       <c r="G101" s="3">
-        <v>-332000</v>
+        <v>-345400</v>
       </c>
       <c r="H101" s="3">
-        <v>-74800</v>
+        <v>-75500</v>
       </c>
       <c r="I101" s="3">
-        <v>-181100</v>
+        <v>-175900</v>
       </c>
       <c r="J101" s="3">
-        <v>-513100</v>
+        <v>-528500</v>
       </c>
       <c r="K101" s="3">
         <v>223300</v>
@@ -4498,25 +4498,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1548400</v>
+        <v>1034300</v>
       </c>
       <c r="E102" s="3">
-        <v>1146900</v>
+        <v>1496500</v>
       </c>
       <c r="F102" s="3">
-        <v>-557700</v>
+        <v>-575500</v>
       </c>
       <c r="G102" s="3">
-        <v>1119300</v>
+        <v>1164600</v>
       </c>
       <c r="H102" s="3">
-        <v>-384500</v>
+        <v>-388100</v>
       </c>
       <c r="I102" s="3">
-        <v>-648200</v>
+        <v>-629600</v>
       </c>
       <c r="J102" s="3">
-        <v>1536600</v>
+        <v>1582800</v>
       </c>
       <c r="K102" s="3">
         <v>-98000</v>

--- a/AAII_Financials/Yearly/BTI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BTI_YR_FIN.xlsx
@@ -656,208 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>32383500</v>
+      </c>
+      <c r="E8" s="3">
         <v>34751900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>33321300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>34777700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>35192000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>34271900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>31215500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>26443200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17529700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15348700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18596800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20317200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19637800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20277200</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5721300</v>
+      </c>
+      <c r="E9" s="3">
         <v>6229900</v>
       </c>
-      <c r="E9" s="3">
-        <v>5788300</v>
-      </c>
       <c r="F9" s="3">
+        <v>5517200</v>
+      </c>
+      <c r="G9" s="3">
         <v>6224600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6071500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5908200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5859000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6802700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4631200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3552600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4033200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4317700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4281800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4511300</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>26662200</v>
+      </c>
+      <c r="E10" s="3">
         <v>28521900</v>
       </c>
-      <c r="E10" s="3">
-        <v>27533000</v>
-      </c>
       <c r="F10" s="3">
+        <v>27804100</v>
+      </c>
+      <c r="G10" s="3">
         <v>28553100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>29120500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>28363700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>25356500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19640500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12898500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11796200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14563600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15999400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15356000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>15765900</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -875,53 +887,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>475700</v>
+      </c>
+      <c r="E12" s="3">
         <v>519700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>389200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>411600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>419100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>498000</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>258200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>65800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>70300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>98500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>121200</v>
       </c>
-      <c r="O12" s="3" t="s">
+      <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>106700</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,99 +980,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>36207800</v>
+        <v>8167600</v>
       </c>
       <c r="E14" s="3">
-        <v>1286800</v>
+        <v>36109700</v>
       </c>
       <c r="F14" s="3">
+        <v>1106100</v>
+      </c>
+      <c r="G14" s="3">
         <v>942400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1369400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1920400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>906200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1284000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>873400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>549300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1099500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>358100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>46500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>686000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2796800</v>
+      </c>
+      <c r="E15" s="3">
         <v>1081400</v>
       </c>
-      <c r="E15" s="3">
-        <v>1159100</v>
-      </c>
       <c r="F15" s="3">
+        <v>1307300</v>
+      </c>
+      <c r="G15" s="3">
         <v>1394700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1488200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1316500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1019600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>977200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1346100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>473200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>640300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>589800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>764100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>679500</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>18650300</v>
+        <v>20119700</v>
       </c>
       <c r="E17" s="3">
-        <v>19281900</v>
+        <v>18785300</v>
       </c>
       <c r="F17" s="3">
+        <v>19462600</v>
+      </c>
+      <c r="G17" s="3">
         <v>20007600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>20251500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>20480800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18429500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16753400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11880000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10132900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12540300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12959800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12692800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14060700</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>16101500</v>
+        <v>12263900</v>
       </c>
       <c r="E18" s="3">
-        <v>14039400</v>
+        <v>15966500</v>
       </c>
       <c r="F18" s="3">
+        <v>13858700</v>
+      </c>
+      <c r="G18" s="3">
         <v>14770100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14940500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13791100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12786000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9689800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5649700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5215800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6056500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7357300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6945000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6216600</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,233 +1212,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-501900</v>
+        <v>-2237200</v>
       </c>
       <c r="E20" s="3">
+        <v>-505700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-331300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-524000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-641700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-864800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-759600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-32875600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2898000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2322700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1179400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1181000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1782800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1023100</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>17684800</v>
+        <v>17297800</v>
       </c>
       <c r="E21" s="3">
-        <v>15529900</v>
+        <v>17553600</v>
       </c>
       <c r="F21" s="3">
+        <v>15497300</v>
+      </c>
+      <c r="G21" s="3">
         <v>16688800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>17070300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>15972500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>14565200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>43542600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9301500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8024500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7933500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9175300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9345300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8311500</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2364100</v>
+        <v>2218400</v>
       </c>
       <c r="E22" s="3">
+        <v>2331000</v>
+      </c>
+      <c r="F22" s="3">
         <v>1960400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1991800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2441200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2368100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2082600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1485400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>800200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>680500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>782700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>817500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1498400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>746600</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4429300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-21731500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11234400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12407200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11839900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10478800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10643500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>39909400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7747500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6858000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6453200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7720800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7229400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6493100</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>446900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3658200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2985700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2964000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2878100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2732300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2728700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-10987400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1744300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1561300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1936800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2130200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1959900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2048900</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3982400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-18073300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8248700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9443200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8961800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7746500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7914800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>50896800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6003300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5296600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4516400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5590500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5269500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4444200</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3788300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-18357400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7972800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9192700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8737900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7554500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7687900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>50665700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5766300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5024900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4146400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5197800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4908800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4075500</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1614,8 +1674,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>501900</v>
+        <v>2237200</v>
       </c>
       <c r="E32" s="3">
+        <v>505700</v>
+      </c>
+      <c r="F32" s="3">
         <v>331300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>524000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>641700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>864800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>759600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>32875600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2898000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2322700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1179400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1181000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1782800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1023100</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3840900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-18300000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8031800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9209000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8737900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7554500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7687900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>50665700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5766300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5024900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4146400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5197800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4908800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4075500</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3840900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-18300000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8031800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9209000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8737900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7554500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7687900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>50665700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5766300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5024900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4146400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5197800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4908800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4075500</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,413 +2073,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6631400</v>
+      </c>
+      <c r="E41" s="3">
         <v>5934400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4152100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3803600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4285700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3345500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3316300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4448200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2734300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2299300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2419900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2803900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1263100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1277300</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>642200</v>
+      </c>
+      <c r="E42" s="3">
         <v>765500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>697600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>617500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>330400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>162900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>226900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>87900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>18600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>41000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>66600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>71900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1460900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1686800</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4595800</v>
+      </c>
+      <c r="E43" s="3">
         <v>4831400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5441300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5508300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5188100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5582400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4667300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6099900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4904100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3912100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3760400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3955600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3650900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3357800</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5778900</v>
+      </c>
+      <c r="E44" s="3">
         <v>6289800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6832900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7148100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>8189100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>8071000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7684100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7925900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7186800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4974500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5501400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5381500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5204900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4606100</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>246600</v>
+      </c>
+      <c r="E45" s="3">
         <v>248400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1442300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>264000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>591200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>418500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>234500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>314900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>488800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>268200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>407300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>459300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>296100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>258100</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17895000</v>
+      </c>
+      <c r="E46" s="3">
         <v>18069500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18566200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17341400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18584500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17580300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16129000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18876800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15332600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11495100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12155600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12672300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11875800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11186100</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2563900</v>
+      </c>
+      <c r="E47" s="3">
         <v>2659600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2579700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2705400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2482100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2479300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2263500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2188300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12590800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8460300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3446200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3336500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3349700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3895100</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5482200</v>
+      </c>
+      <c r="E48" s="3">
         <v>5837600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5864200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6706700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6908400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7308100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6584200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6598600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4541800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3538500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3998600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4201900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4138300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4012300</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>118026500</v>
+      </c>
+      <c r="E49" s="3">
         <v>121722600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>155521400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>156563100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>157477700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>157323400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>158056900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>159201200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15032400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12223700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14381200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14918300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15138800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15790900</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,54 +2598,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1663800</v>
+      </c>
+      <c r="E52" s="3">
         <v>1765400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1653100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1856400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1806300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1496600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3043600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3337200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1844800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1195900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>849200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>660400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>826100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>825600</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>148852600</v>
+      </c>
+      <c r="E54" s="3">
         <v>151215200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>185006300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>186000400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>187988100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>186749200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>186515600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>190652200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>49342400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36913500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>34830900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35789400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35328600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>35710000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,278 +2785,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2139500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2174300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2243500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5312000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5081600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4573200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4533500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3106000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9099800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6954000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7353000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7643600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7533200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6813100</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5398300</v>
+      </c>
+      <c r="E58" s="3">
         <v>5507700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5334100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5405400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5517200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10015200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5384800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7329900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3730500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2571000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3299800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2636200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2115000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2325500</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15913200</v>
+      </c>
+      <c r="E59" s="3">
         <v>12265000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13916500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9769500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10501900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10322500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10871600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10623800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1878300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1023700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1019600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>952000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>877800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1194300</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23464800</v>
+      </c>
+      <c r="E60" s="3">
         <v>19963600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>21510900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20505900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>21132100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>24929500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20811600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21092100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14708600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10548700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11672400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11231700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10526100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10332900</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>40860300</v>
+      </c>
+      <c r="E61" s="3">
         <v>45336800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>47184800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>48293900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>54512300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>50068200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>55166300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>59508000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20455000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>17342300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13016800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12935900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11742600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11205900</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6250900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1801100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1704900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1930900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2016500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2244900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2018800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2015300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3750300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3128500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2402600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2388500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3003200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3012800</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>86262600</v>
+      </c>
+      <c r="E66" s="3">
         <v>83790200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>93784000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>94735400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>102035700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>101774700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>102795000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>108228700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>39191800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>31181200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>27496500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26956900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>25668700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>24955800</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3230,20 +3397,20 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
         <v>122900</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>119200</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>114700</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>121600</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>32572600</v>
+      </c>
+      <c r="E72" s="3">
         <v>40285100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>61686800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>66801200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>64429900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>60254300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>55822600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>56944000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9419900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5047100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6561000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8064300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12568700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12030200</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>62149300</v>
+      </c>
+      <c r="E76" s="3">
         <v>66956200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>90810300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>90858700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>85444500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>84513600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>83294900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>82001800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10150600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5732300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7334400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8832500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9659900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10754200</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3840900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-18300000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8031800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9209000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8737900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7554500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7687900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>50665700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5766300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5024900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4146400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5197800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4908800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4075500</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,53 +3886,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>578400</v>
+      </c>
+      <c r="E83" s="3">
         <v>626700</v>
       </c>
-      <c r="E83" s="3">
-        <v>632600</v>
-      </c>
       <c r="F83" s="3">
+        <v>754300</v>
+      </c>
+      <c r="G83" s="3">
         <v>769100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>820500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1316500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1019600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>977200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>753000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>501300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>696200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>635100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>614100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1075800</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12675700</v>
+      </c>
+      <c r="E89" s="3">
         <v>13647000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12523600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13157400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13360800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11914400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13121200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7227100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5719200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5528500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4946400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5906100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5723300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6012500</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-608400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-585900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-630200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-713600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-697700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-879400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-966100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1069100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-727000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-565700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-704200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-764200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-858400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-671600</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1721400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-377000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-849400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1543600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1069000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-846300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1301300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-25064500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-794000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4674700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-625600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-446000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-517100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-937600</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,53 +4454,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>6596400</v>
+      </c>
+      <c r="E96" s="3">
         <v>6514000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>5994300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>6648400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>6478300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>6089700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>4260700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>4683400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-3610100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3244500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3609900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3476300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3281200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3105000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,142 +4643,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13310500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11863800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10697000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11846700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10781800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11380700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-12273600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>19948600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5246500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-256500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4614900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5281700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5111800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5329000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-351800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-371900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>519300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-342600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-345400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-75500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-175900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-528500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>223300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-318600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-83900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-262300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-227500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-63200</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>734900</v>
+      </c>
+      <c r="E102" s="3">
         <v>1034300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1496500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-575500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1164600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-388100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-629600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1582800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-98000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>278800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-378000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-83900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-133200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-317300</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BTI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BTI_YR_FIN.xlsx
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>34468400</v>
+      </c>
+      <c r="E8" s="3">
         <v>32383500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>34751900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>33321300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>34777700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>35192000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>34271900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>31215500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>26443200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17529700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15348700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18596800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20317200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19637800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20277200</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5979800</v>
+      </c>
+      <c r="E9" s="3">
         <v>5721300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6229900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5517200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6224600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6071500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5908200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5859000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6802700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4631200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3552600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4033200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4317700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4281800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4511300</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>28488600</v>
+      </c>
+      <c r="E10" s="3">
         <v>26662200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>28521900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>27804100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>28553100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>29120500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>28363700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25356500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19640500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12898500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11796200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14563600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15999400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>15356000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>15765900</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -888,56 +900,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>481800</v>
+      </c>
+      <c r="E12" s="3">
         <v>475700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>519700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>389200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>411600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>419100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>498000</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>258200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>65800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>70300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>98500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>121200</v>
       </c>
-      <c r="P12" s="3" t="s">
+      <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>106700</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,105 +999,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-387600</v>
+      </c>
+      <c r="E14" s="3">
         <v>8167600</v>
       </c>
-      <c r="E14" s="3">
-        <v>36109700</v>
-      </c>
       <c r="F14" s="3">
+        <v>6678300</v>
+      </c>
+      <c r="G14" s="3">
         <v>1106100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>942400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1369400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1920400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>906200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1284000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>873400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>549300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1099500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>358100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>46500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>686000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2979800</v>
+      </c>
+      <c r="E15" s="3">
         <v>2796800</v>
       </c>
-      <c r="E15" s="3">
-        <v>1081400</v>
-      </c>
       <c r="F15" s="3">
+        <v>30520500</v>
+      </c>
+      <c r="G15" s="3">
         <v>1307300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1394700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1488200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1316500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1019600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>977200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1346100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>473200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>640300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>589800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>764100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>679500</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21337800</v>
+      </c>
+      <c r="E17" s="3">
         <v>20119700</v>
       </c>
-      <c r="E17" s="3">
-        <v>18785300</v>
-      </c>
       <c r="F17" s="3">
+        <v>48216700</v>
+      </c>
+      <c r="G17" s="3">
         <v>19462600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>20007600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>20251500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20480800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18429500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16753400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11880000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10132900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12540300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12959800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12692800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14060700</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>13130600</v>
+      </c>
+      <c r="E18" s="3">
         <v>12263900</v>
       </c>
-      <c r="E18" s="3">
-        <v>15966500</v>
-      </c>
       <c r="F18" s="3">
+        <v>-13464900</v>
+      </c>
+      <c r="G18" s="3">
         <v>13858700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14770100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>14940500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>13791100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>12786000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9689800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5649700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5215800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6056500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7357300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6945000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6216600</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,248 +1245,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1850600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2237200</v>
       </c>
-      <c r="E20" s="3">
-        <v>-505700</v>
-      </c>
       <c r="F20" s="3">
+        <v>-508200</v>
+      </c>
+      <c r="G20" s="3">
         <v>-331300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-524000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-641700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-864800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-759600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-32875600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2898000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2322700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1179400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1181000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1782800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1023100</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>17961000</v>
+      </c>
+      <c r="E21" s="3">
         <v>17297800</v>
       </c>
-      <c r="E21" s="3">
-        <v>17553600</v>
-      </c>
       <c r="F21" s="3">
+        <v>17563800</v>
+      </c>
+      <c r="G21" s="3">
         <v>15497300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>16688800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>17070300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>15972500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>14565200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>43542600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9301500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8024500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7933500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9175300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9345300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8311500</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2387600</v>
+      </c>
+      <c r="E22" s="3">
         <v>2218400</v>
       </c>
-      <c r="E22" s="3">
-        <v>2331000</v>
-      </c>
       <c r="F22" s="3">
+        <v>2333500</v>
+      </c>
+      <c r="G22" s="3">
         <v>1960400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1991800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2441200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2368100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2082600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1485400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>800200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>680500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>782700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>817500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1498400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>746600</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>13269200</v>
+      </c>
+      <c r="E23" s="3">
         <v>4429300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-21731500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11234400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12407200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11839900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10478800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10643500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>39909400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7747500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6858000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6453200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7720800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7229400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6493100</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2818300</v>
+      </c>
+      <c r="E24" s="3">
         <v>446900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3658200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2985700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2964000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2878100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2732300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2728700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-10987400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1744300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1561300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1936800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2130200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1959900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2048900</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10450900</v>
+      </c>
+      <c r="E26" s="3">
         <v>3982400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-18073300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8248700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9443200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8961800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7746500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7914800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>50896800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6003300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5296600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4516400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5590500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5269500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4444200</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10332400</v>
+      </c>
+      <c r="E27" s="3">
         <v>3788300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-18357400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7972800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>9192700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8737900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7554500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7687900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>50665700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5766300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5024900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4146400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5197800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4908800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4075500</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,8 +1737,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>8</v>
@@ -1692,9 +1752,12 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1850600</v>
+      </c>
+      <c r="E32" s="3">
         <v>2237200</v>
       </c>
-      <c r="E32" s="3">
-        <v>505700</v>
-      </c>
       <c r="F32" s="3">
+        <v>508200</v>
+      </c>
+      <c r="G32" s="3">
         <v>331300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>524000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>641700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>864800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>759600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>32875600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2898000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2322700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1179400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1181000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1782800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1023100</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10449500</v>
+      </c>
+      <c r="E33" s="3">
         <v>3840900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-18300000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8031800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9209000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8737900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7554500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7687900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>50665700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5766300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5024900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4146400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5197800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4908800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4075500</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10449500</v>
+      </c>
+      <c r="E35" s="3">
         <v>3840900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-18300000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8031800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9209000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8737900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7554500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7687900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>50665700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5766300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5024900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4146400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5197800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4908800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4075500</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,440 +2159,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5150700</v>
+      </c>
+      <c r="E41" s="3">
         <v>6631400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5934400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4152100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3803600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4285700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3345500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3316300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4448200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2734300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2299300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2419900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2803900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1263100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1277300</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E42" s="3">
         <v>642200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>765500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>697600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>617500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>330400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>162900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>226900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>87900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>18600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>41000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>66600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>71900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1460900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1686800</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5749700</v>
+      </c>
+      <c r="E43" s="3">
         <v>4595800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4831400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5441300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5508300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5188100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5582400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4667300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6099900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4904100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3912100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3760400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3955600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3650900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3357800</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5897700</v>
+      </c>
+      <c r="E44" s="3">
         <v>5778900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6289800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6832900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7148100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>8189100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8071000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7684100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7925900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7186800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4974500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5501400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5381500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5204900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4606100</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>251700</v>
+      </c>
+      <c r="E45" s="3">
         <v>246600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>248400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1442300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>264000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>591200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>418500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>234500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>314900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>488800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>268200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>407300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>459300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>296100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>258100</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17071300</v>
+      </c>
+      <c r="E46" s="3">
         <v>17895000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18069500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18566200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17341400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18584500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17580300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16129000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18876800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15332600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11495100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12155600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12672300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11875800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11186100</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2495300</v>
+      </c>
+      <c r="E47" s="3">
         <v>2563900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2659600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2579700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2705400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2482100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2479300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2263500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2188300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>12590800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8460300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3446200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3336500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3349700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3895100</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6033600</v>
+      </c>
+      <c r="E48" s="3">
         <v>5482200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5837600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5864200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6706700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6908400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7308100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6584200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6598600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4541800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3538500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3998600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4201900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4138300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4012300</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>117004000</v>
+      </c>
+      <c r="E49" s="3">
         <v>118026500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>121722600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>155521400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>156563100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>157477700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>157323400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>158056900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>159201200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15032400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12223700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14381200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14918300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15138800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15790900</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,57 +2717,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1753700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1663800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1765400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1653100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1856400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1806300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1496600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3043600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3337200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1844800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1195900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>849200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>660400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>826100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>825600</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>147092900</v>
+      </c>
+      <c r="E54" s="3">
         <v>148852600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>151215200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>185006300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>186000400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>187988100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>186749200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>186515600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>190652200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>49342400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36913500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>34830900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35789400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>35328600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>35710000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,296 +2915,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2441500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2139500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2174300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2243500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5312000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5081600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4573200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4533500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3106000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9099800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6954000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7353000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7643600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7533200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6813100</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4524900</v>
+      </c>
+      <c r="E58" s="3">
         <v>5398300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5507700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5334100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5405400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5517200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10015200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5384800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7329900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3730500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2571000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3299800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2636200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2115000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2325500</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12566600</v>
+      </c>
+      <c r="E59" s="3">
         <v>15913200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12265000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13916500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9769500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10501900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10322500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10871600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10623800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1878300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1023700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1019600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>952000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>877800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1194300</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19547800</v>
+      </c>
+      <c r="E60" s="3">
         <v>23464800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19963600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21510900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20505900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>21132100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>24929500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20811600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>21092100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14708600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10548700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11672400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11231700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10526100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10332900</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>42675600</v>
+      </c>
+      <c r="E61" s="3">
         <v>40860300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>45336800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>47184800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>48293900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>54512300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>50068200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>55166300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>59508000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>20455000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>17342300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13016800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12935900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11742600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11205900</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5040400</v>
+      </c>
+      <c r="E62" s="3">
         <v>6250900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1801100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1704900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1930900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2016500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2244900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2018800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2015300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3750300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3128500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2402600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2388500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3003200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3012800</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>82294800</v>
+      </c>
+      <c r="E66" s="3">
         <v>86262600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>83790200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>93784000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>94735400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>102035700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>101774700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>102795000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>108228700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>39191800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>31181200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27496500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>26956900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>25668700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>24955800</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3400,20 +3567,20 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>122900</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>119200</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>114700</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>121600</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>36759100</v>
+      </c>
+      <c r="E72" s="3">
         <v>32572600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>40285100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>61686800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>66801200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>64429900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>60254300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>55822600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>56944000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9419900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5047100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6561000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8064300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12568700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12030200</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>64503400</v>
+      </c>
+      <c r="E76" s="3">
         <v>62149300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>66956200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>90810300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>90858700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>85444500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>84513600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>83294900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>82001800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10150600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5732300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7334400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8832500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9659900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10754200</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10449500</v>
+      </c>
+      <c r="E81" s="3">
         <v>3840900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-18300000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8031800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9209000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8737900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7554500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7687900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>50665700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5766300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5024900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4146400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5197800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4908800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4075500</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>659500</v>
+      </c>
+      <c r="E83" s="3">
         <v>578400</v>
       </c>
-      <c r="E83" s="3">
-        <v>626700</v>
-      </c>
       <c r="F83" s="3">
+        <v>769300</v>
+      </c>
+      <c r="G83" s="3">
         <v>754300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>769100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>820500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1316500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1019600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>977200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>753000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>501300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>696200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>635100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>614100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1075800</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8535700</v>
+      </c>
+      <c r="E89" s="3">
         <v>12675700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13647000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>12523600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13157400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13360800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11914400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13121200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7227100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5719200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5528500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4946400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5906100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5723300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6012500</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-741600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-608400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-585900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-630200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-713600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-697700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-879400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-966100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1069100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-727000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-565700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-704200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-764200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-858400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-671600</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1866800</v>
+      </c>
+      <c r="E94" s="3">
         <v>1721400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-377000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-849400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1543600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1069000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-846300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1301300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-25064500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-794000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4674700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-625600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-446000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-517100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-937600</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,56 +4687,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>7122500</v>
+      </c>
+      <c r="E96" s="3">
         <v>6596400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>6514000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>5994300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>6648400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>6478300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>6089700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>4260700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>4683400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3610100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3244500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3609900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3476300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3281200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3105000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,151 +4888,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11792700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13310500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11863800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10697000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11846700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10781800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-11380700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-12273600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>19948600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5246500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-256500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4614900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5281700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5111800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5329000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-102300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-351800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-371900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>519300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-342600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-345400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-75500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-175900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-528500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>223300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-318600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-83900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-262300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-227500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-63200</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1492600</v>
+      </c>
+      <c r="E102" s="3">
         <v>734900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1034300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1496500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-575500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1164600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-388100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-629600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1582800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-98000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>278800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-378000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-83900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-133200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-317300</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
